--- a/artfynd/A 34188-2024 artfynd.xlsx
+++ b/artfynd/A 34188-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121895118</v>
+        <v>121895115</v>
       </c>
       <c r="B2" t="n">
-        <v>57726</v>
+        <v>57357</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -710,12 +710,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -725,14 +725,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gotjärnet, Gotjärnet, Vrm</t>
+          <t>Noret, Noret, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>357602</v>
+        <v>357630</v>
       </c>
       <c r="R2" t="n">
-        <v>6629595</v>
+        <v>6629504</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -767,6 +767,11 @@
           <t>2024-12-30</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Såg endast en glimt av den och kunde inte säkert säga om det var Större Hackspett eller Tretåig. Men det lutade mer åt tretåig samt att en hel del skalade granar fanns i området. Och  många tecken på hackspettsaktivitet med hackhål i diverse torrakor.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -778,7 +783,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Barrskog i branter</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -932,10 +937,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121895115</v>
+        <v>121895118</v>
       </c>
       <c r="B4" t="n">
-        <v>57357</v>
+        <v>57726</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -944,20 +949,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -967,12 +972,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -982,14 +987,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Noret, Noret, Vrm</t>
+          <t>Gotjärnet, Gotjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>357630</v>
+        <v>357602</v>
       </c>
       <c r="R4" t="n">
-        <v>6629504</v>
+        <v>6629595</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -1024,11 +1029,6 @@
           <t>2024-12-30</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Såg endast en glimt av den och kunde inte säkert säga om det var Större Hackspett eller Tretåig. Men det lutade mer åt tretåig samt att en hel del skalade granar fanns i området. Och  många tecken på hackspettsaktivitet med hackhål i diverse torrakor.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1040,7 +1040,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Barrskog i branter</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 34188-2024 artfynd.xlsx
+++ b/artfynd/A 34188-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121895115</v>
+        <v>121895128</v>
       </c>
       <c r="B2" t="n">
-        <v>57357</v>
+        <v>57510</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,36 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -729,13 +734,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>357630</v>
+        <v>357721</v>
       </c>
       <c r="R2" t="n">
-        <v>6629504</v>
+        <v>6629323</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -762,14 +767,19 @@
           <t>2024-12-30</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-12-30</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Såg endast en glimt av den och kunde inte säkert säga om det var Större Hackspett eller Tretåig. Men det lutade mer åt tretåig samt att en hel del skalade granar fanns i området. Och  många tecken på hackspettsaktivitet med hackhål i diverse torrakor.</t>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,7 +793,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -801,10 +811,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121895128</v>
+        <v>121895118</v>
       </c>
       <c r="B3" t="n">
-        <v>57510</v>
+        <v>57726</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,35 +823,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -856,17 +861,17 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Noret, Noret, Vrm</t>
+          <t>Gotjärnet, Gotjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>357721</v>
+        <v>357602</v>
       </c>
       <c r="R3" t="n">
-        <v>6629323</v>
+        <v>6629595</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -893,21 +898,11 @@
           <t>2024-12-30</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-12-30</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -919,7 +914,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrskog i branter</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -937,10 +932,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121895118</v>
+        <v>121895115</v>
       </c>
       <c r="B4" t="n">
-        <v>57726</v>
+        <v>57357</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -949,20 +944,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -972,12 +967,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -987,14 +982,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gotjärnet, Gotjärnet, Vrm</t>
+          <t>Noret, Noret, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>357602</v>
+        <v>357630</v>
       </c>
       <c r="R4" t="n">
-        <v>6629595</v>
+        <v>6629504</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -1029,6 +1024,11 @@
           <t>2024-12-30</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Såg endast en glimt av den och kunde inte säkert säga om det var Större Hackspett eller Tretåig. Men det lutade mer åt tretåig samt att en hel del skalade granar fanns i området. Och  många tecken på hackspettsaktivitet med hackhål i diverse torrakor.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1040,7 +1040,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Barrskog i branter</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1055,6 +1055,686 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121942431</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91168</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Gotjärnet, Gotjärnet, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>357652</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6629580</v>
+      </c>
+      <c r="S5" t="n">
+        <v>20</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Hjälp gärna till att artbestämma. Är ingen höjdare på vedsvampar?</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Petrus Oledal</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Petrus Oledal</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121942119</v>
+      </c>
+      <c r="B6" t="n">
+        <v>94635</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2818</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>utan kapsel</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Gotjärnet, Gotjärnet, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>357630</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6629615</v>
+      </c>
+      <c r="S6" t="n">
+        <v>20</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-01-04</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-01-04</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Stump</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Petrus Oledal</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Petrus Oledal</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121941985</v>
+      </c>
+      <c r="B7" t="n">
+        <v>94731</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>210</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Buxbaumia viridis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Gotjärnet, Gotjärnet, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>357622</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6629654</v>
+      </c>
+      <c r="S7" t="n">
+        <v>20</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Stump</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Petrus Oledal</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Petrus Oledal</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>121942079</v>
+      </c>
+      <c r="B8" t="n">
+        <v>94635</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>2818</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Gotjärnet, Gotjärnet, Vrm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>357610</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6629638</v>
+      </c>
+      <c r="S8" t="n">
+        <v>20</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Stump</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Petrus Oledal</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Petrus Oledal</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>121942525</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57373</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Gotjärnet, Gotjärnet, Vrm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>357594</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6629645</v>
+      </c>
+      <c r="S9" t="n">
+        <v>20</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Hörde en spillkråka i närheten och dessaTydliga spår efter spillkråka som sökt föda.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Petrus Oledal</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Petrus Oledal</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34188-2024 artfynd.xlsx
+++ b/artfynd/A 34188-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121895128</v>
+        <v>121895115</v>
       </c>
       <c r="B2" t="n">
-        <v>57510</v>
+        <v>57357</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,36 +691,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -734,13 +729,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>357721</v>
+        <v>357630</v>
       </c>
       <c r="R2" t="n">
-        <v>6629323</v>
+        <v>6629504</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -767,19 +762,14 @@
           <t>2024-12-30</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-12-30</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>14:30</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Såg endast en glimt av den och kunde inte säkert säga om det var Större Hackspett eller Tretåig. Men det lutade mer åt tretåig samt att en hel del skalade granar fanns i området. Och  många tecken på hackspettsaktivitet med hackhål i diverse torrakor.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -793,7 +783,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -811,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121895118</v>
+        <v>121895128</v>
       </c>
       <c r="B3" t="n">
-        <v>57726</v>
+        <v>57510</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -823,30 +813,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -861,17 +856,17 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gotjärnet, Gotjärnet, Vrm</t>
+          <t>Noret, Noret, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>357602</v>
+        <v>357721</v>
       </c>
       <c r="R3" t="n">
-        <v>6629595</v>
+        <v>6629323</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -898,11 +893,21 @@
           <t>2024-12-30</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-12-30</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -914,7 +919,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Barrskog i branter</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -932,10 +937,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121895115</v>
+        <v>121895118</v>
       </c>
       <c r="B4" t="n">
-        <v>57357</v>
+        <v>57726</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -944,20 +949,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -967,12 +972,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -982,14 +987,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Noret, Noret, Vrm</t>
+          <t>Gotjärnet, Gotjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>357630</v>
+        <v>357602</v>
       </c>
       <c r="R4" t="n">
-        <v>6629504</v>
+        <v>6629595</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -1024,11 +1029,6 @@
           <t>2024-12-30</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Såg endast en glimt av den och kunde inte säkert säga om det var Större Hackspett eller Tretåig. Men det lutade mer åt tretåig samt att en hel del skalade granar fanns i området. Och  många tecken på hackspettsaktivitet med hackhål i diverse torrakor.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1040,7 +1040,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Barrskog i branter</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1058,10 +1058,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121942431</v>
+        <v>121942525</v>
       </c>
       <c r="B5" t="n">
-        <v>91168</v>
+        <v>57373</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1070,25 +1070,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1096,9 +1096,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1107,10 +1107,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>357652</v>
+        <v>357594</v>
       </c>
       <c r="R5" t="n">
-        <v>6629580</v>
+        <v>6629645</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1157,7 +1157,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Hjälp gärna till att artbestämma. Är ingen höjdare på vedsvampar?</t>
+          <t>Hörde en spillkråka i närheten och dessaTydliga spår efter spillkråka som sökt föda.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1171,27 +1171,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Picea abies</t>
+          <t>Blandskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1209,10 +1189,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121942119</v>
+        <v>121942431</v>
       </c>
       <c r="B6" t="n">
-        <v>94635</v>
+        <v>91168</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1221,25 +1201,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2818</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1249,12 +1229,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>utan kapsel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1263,10 +1238,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>357630</v>
+        <v>357652</v>
       </c>
       <c r="R6" t="n">
-        <v>6629615</v>
+        <v>6629580</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1293,12 +1268,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-01-04</t>
+          <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-01-04</t>
+          <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Hjälp gärna till att artbestämma. Är ingen höjdare på vedsvampar?</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1315,14 +1305,24 @@
           <t>Gransumpskog</t>
         </is>
       </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Stump</t>
+          <t>Bark of dead wood # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1340,10 +1340,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121941985</v>
+        <v>121942119</v>
       </c>
       <c r="B7" t="n">
-        <v>94731</v>
+        <v>94635</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1356,21 +1356,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>210</v>
+        <v>2818</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1380,7 +1380,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>kapslar</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>utan kapsel</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1389,10 +1394,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>357622</v>
+        <v>357630</v>
       </c>
       <c r="R7" t="n">
-        <v>6629654</v>
+        <v>6629615</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1419,12 +1424,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2025-01-04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2025-01-04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1438,7 +1443,7 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Blandskog</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -1473,7 +1478,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1607,37 +1612,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121942525</v>
+        <v>121941985</v>
       </c>
       <c r="B9" t="n">
-        <v>57373</v>
+        <v>94731</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>210</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1645,9 +1650,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1656,10 +1661,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>357594</v>
+        <v>357622</v>
       </c>
       <c r="R9" t="n">
-        <v>6629645</v>
+        <v>6629654</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1689,26 +1694,11 @@
           <t>2024-12-30</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-12-30</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Hörde en spillkråka i närheten och dessaTydliga spår efter spillkråka som sökt föda.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1721,6 +1711,16 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Stump</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>

--- a/artfynd/A 34188-2024 artfynd.xlsx
+++ b/artfynd/A 34188-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121895115</v>
+        <v>121895128</v>
       </c>
       <c r="B2" t="n">
-        <v>57357</v>
+        <v>57510</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,36 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -729,13 +734,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>357630</v>
+        <v>357721</v>
       </c>
       <c r="R2" t="n">
-        <v>6629504</v>
+        <v>6629323</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -762,14 +767,19 @@
           <t>2024-12-30</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-12-30</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Såg endast en glimt av den och kunde inte säkert säga om det var Större Hackspett eller Tretåig. Men det lutade mer åt tretåig samt att en hel del skalade granar fanns i området. Och  många tecken på hackspettsaktivitet med hackhål i diverse torrakor.</t>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,7 +793,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -801,10 +811,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121895128</v>
+        <v>121895115</v>
       </c>
       <c r="B3" t="n">
-        <v>57510</v>
+        <v>57357</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,36 +827,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -860,13 +865,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>357721</v>
+        <v>357630</v>
       </c>
       <c r="R3" t="n">
-        <v>6629323</v>
+        <v>6629504</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -893,19 +898,14 @@
           <t>2024-12-30</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-12-30</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:30</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Såg endast en glimt av den och kunde inte säkert säga om det var Större Hackspett eller Tretåig. Men det lutade mer åt tretåig samt att en hel del skalade granar fanns i området. Och  många tecken på hackspettsaktivitet med hackhål i diverse torrakor.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,7 +919,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -1058,10 +1058,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121942525</v>
+        <v>121942431</v>
       </c>
       <c r="B5" t="n">
-        <v>57373</v>
+        <v>91168</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1070,25 +1070,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1096,9 +1096,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1107,10 +1107,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>357594</v>
+        <v>357652</v>
       </c>
       <c r="R5" t="n">
-        <v>6629645</v>
+        <v>6629580</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1157,7 +1157,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Hörde en spillkråka i närheten och dessaTydliga spår efter spillkråka som sökt föda.</t>
+          <t>Hjälp gärna till att artbestämma. Är ingen höjdare på vedsvampar?</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1171,7 +1171,27 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Blandskog</t>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1189,10 +1209,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121942431</v>
+        <v>121942525</v>
       </c>
       <c r="B6" t="n">
-        <v>91168</v>
+        <v>57373</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1201,25 +1221,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1227,9 +1247,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1238,10 +1258,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>357652</v>
+        <v>357594</v>
       </c>
       <c r="R6" t="n">
-        <v>6629580</v>
+        <v>6629645</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1288,7 +1308,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Hjälp gärna till att artbestämma. Är ingen höjdare på vedsvampar?</t>
+          <t>Hörde en spillkråka i närheten och dessaTydliga spår efter spillkråka som sökt föda.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1302,27 +1322,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Picea abies</t>
+          <t>Blandskog</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>

--- a/artfynd/A 34188-2024 artfynd.xlsx
+++ b/artfynd/A 34188-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121895128</v>
+        <v>121895118</v>
       </c>
       <c r="B2" t="n">
-        <v>57510</v>
+        <v>57734</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -730,17 +725,17 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Noret, Noret, Vrm</t>
+          <t>Gotjärnet, Gotjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>357721</v>
+        <v>357602</v>
       </c>
       <c r="R2" t="n">
-        <v>6629323</v>
+        <v>6629595</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -767,21 +762,11 @@
           <t>2024-12-30</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-12-30</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -793,7 +778,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrskog i branter</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -814,7 +799,7 @@
         <v>121895115</v>
       </c>
       <c r="B3" t="n">
-        <v>57357</v>
+        <v>57365</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -937,10 +922,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121895118</v>
+        <v>121895128</v>
       </c>
       <c r="B4" t="n">
-        <v>57726</v>
+        <v>57518</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -949,30 +934,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -987,17 +977,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gotjärnet, Gotjärnet, Vrm</t>
+          <t>Noret, Noret, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>357602</v>
+        <v>357721</v>
       </c>
       <c r="R4" t="n">
-        <v>6629595</v>
+        <v>6629323</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1024,11 +1014,21 @@
           <t>2024-12-30</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-12-30</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1040,7 +1040,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Barrskog i branter</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1058,10 +1058,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121942431</v>
+        <v>121942119</v>
       </c>
       <c r="B5" t="n">
-        <v>91168</v>
+        <v>94653</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1070,25 +1070,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>2818</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1098,7 +1098,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>utan kapsel</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1107,10 +1112,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>357652</v>
+        <v>357630</v>
       </c>
       <c r="R5" t="n">
-        <v>6629580</v>
+        <v>6629615</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1137,27 +1142,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2025-01-04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Hjälp gärna till att artbestämma. Är ingen höjdare på vedsvampar?</t>
+          <t>2025-01-04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1174,24 +1164,14 @@
           <t>Gransumpskog</t>
         </is>
       </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Picea abies</t>
+          <t>Stump</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1209,10 +1189,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121942525</v>
+        <v>121942431</v>
       </c>
       <c r="B6" t="n">
-        <v>57373</v>
+        <v>91182</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1221,25 +1201,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1247,9 +1227,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1258,10 +1238,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>357594</v>
+        <v>357652</v>
       </c>
       <c r="R6" t="n">
-        <v>6629645</v>
+        <v>6629580</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1308,7 +1288,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Hörde en spillkråka i närheten och dessaTydliga spår efter spillkråka som sökt föda.</t>
+          <t>Hjälp gärna till att artbestämma. Är ingen höjdare på vedsvampar?</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1322,7 +1302,27 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Blandskog</t>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1340,10 +1340,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121942119</v>
+        <v>121942525</v>
       </c>
       <c r="B7" t="n">
-        <v>94635</v>
+        <v>57381</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1352,25 +1352,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2818</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1378,14 +1378,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>utan kapsel</t>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1394,10 +1389,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>357630</v>
+        <v>357594</v>
       </c>
       <c r="R7" t="n">
-        <v>6629615</v>
+        <v>6629645</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1424,12 +1419,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-01-04</t>
+          <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-01-04</t>
+          <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Hörde en spillkråka i närheten och dessaTydliga spår efter spillkråka som sökt föda.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1443,17 +1453,7 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Stump</t>
+          <t>Blandskog</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1474,7 +1474,7 @@
         <v>121942079</v>
       </c>
       <c r="B8" t="n">
-        <v>94635</v>
+        <v>94653</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
         <v>121941985</v>
       </c>
       <c r="B9" t="n">
-        <v>94731</v>
+        <v>94749</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 34188-2024 artfynd.xlsx
+++ b/artfynd/A 34188-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121895118</v>
+        <v>121895128</v>
       </c>
       <c r="B2" t="n">
-        <v>57734</v>
+        <v>57518</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -725,17 +730,17 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gotjärnet, Gotjärnet, Vrm</t>
+          <t>Noret, Noret, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>357602</v>
+        <v>357721</v>
       </c>
       <c r="R2" t="n">
-        <v>6629595</v>
+        <v>6629323</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -762,11 +767,21 @@
           <t>2024-12-30</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-12-30</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -778,7 +793,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Barrskog i branter</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -922,10 +937,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121895128</v>
+        <v>121895118</v>
       </c>
       <c r="B4" t="n">
-        <v>57518</v>
+        <v>57734</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,35 +949,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -977,17 +987,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Noret, Noret, Vrm</t>
+          <t>Gotjärnet, Gotjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>357721</v>
+        <v>357602</v>
       </c>
       <c r="R4" t="n">
-        <v>6629323</v>
+        <v>6629595</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1014,21 +1024,11 @@
           <t>2024-12-30</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-12-30</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1040,7 +1040,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrskog i branter</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1061,7 +1061,7 @@
         <v>121942119</v>
       </c>
       <c r="B5" t="n">
-        <v>94653</v>
+        <v>94655</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1189,10 +1189,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121942431</v>
+        <v>121942525</v>
       </c>
       <c r="B6" t="n">
-        <v>91182</v>
+        <v>57381</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1201,25 +1201,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1227,9 +1227,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1238,10 +1238,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>357652</v>
+        <v>357594</v>
       </c>
       <c r="R6" t="n">
-        <v>6629580</v>
+        <v>6629645</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Hjälp gärna till att artbestämma. Är ingen höjdare på vedsvampar?</t>
+          <t>Hörde en spillkråka i närheten och dessaTydliga spår efter spillkråka som sökt föda.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1302,27 +1302,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Picea abies</t>
+          <t>Blandskog</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1340,10 +1320,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121942525</v>
+        <v>121942431</v>
       </c>
       <c r="B7" t="n">
-        <v>57381</v>
+        <v>91184</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1352,25 +1332,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1378,9 +1358,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1389,10 +1369,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>357594</v>
+        <v>357652</v>
       </c>
       <c r="R7" t="n">
-        <v>6629645</v>
+        <v>6629580</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1439,7 +1419,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Hörde en spillkråka i närheten och dessaTydliga spår efter spillkråka som sökt föda.</t>
+          <t>Hjälp gärna till att artbestämma. Är ingen höjdare på vedsvampar?</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1453,7 +1433,27 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Blandskog</t>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1474,7 +1474,7 @@
         <v>121942079</v>
       </c>
       <c r="B8" t="n">
-        <v>94653</v>
+        <v>94655</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
         <v>121941985</v>
       </c>
       <c r="B9" t="n">
-        <v>94749</v>
+        <v>94751</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 34188-2024 artfynd.xlsx
+++ b/artfynd/A 34188-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121895128</v>
+        <v>121895115</v>
       </c>
       <c r="B2" t="n">
-        <v>57518</v>
+        <v>57365</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,36 +691,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -734,13 +729,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>357721</v>
+        <v>357630</v>
       </c>
       <c r="R2" t="n">
-        <v>6629323</v>
+        <v>6629504</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -767,19 +762,14 @@
           <t>2024-12-30</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-12-30</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>14:30</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Såg endast en glimt av den och kunde inte säkert säga om det var Större Hackspett eller Tretåig. Men det lutade mer åt tretåig samt att en hel del skalade granar fanns i området. Och  många tecken på hackspettsaktivitet med hackhål i diverse torrakor.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -793,7 +783,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -811,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121895115</v>
+        <v>121895128</v>
       </c>
       <c r="B3" t="n">
-        <v>57365</v>
+        <v>57518</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -827,31 +817,36 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -865,13 +860,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>357630</v>
+        <v>357721</v>
       </c>
       <c r="R3" t="n">
-        <v>6629504</v>
+        <v>6629323</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -898,14 +893,19 @@
           <t>2024-12-30</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-12-30</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Såg endast en glimt av den och kunde inte säkert säga om det var Större Hackspett eller Tretåig. Men det lutade mer åt tretåig samt att en hel del skalade granar fanns i området. Och  många tecken på hackspettsaktivitet med hackhål i diverse torrakor.</t>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,7 +919,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -1058,10 +1058,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121942119</v>
+        <v>121942525</v>
       </c>
       <c r="B5" t="n">
-        <v>94655</v>
+        <v>57381</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1070,25 +1070,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2818</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1096,14 +1096,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>utan kapsel</t>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1112,10 +1107,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>357630</v>
+        <v>357594</v>
       </c>
       <c r="R5" t="n">
-        <v>6629615</v>
+        <v>6629645</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1142,12 +1137,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-01-04</t>
+          <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-01-04</t>
+          <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Hörde en spillkråka i närheten och dessaTydliga spår efter spillkråka som sökt föda.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1161,17 +1171,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Stump</t>
+          <t>Blandskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1189,10 +1189,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121942525</v>
+        <v>121942431</v>
       </c>
       <c r="B6" t="n">
-        <v>57381</v>
+        <v>91185</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1201,25 +1201,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1227,9 +1227,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1238,10 +1238,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>357594</v>
+        <v>357652</v>
       </c>
       <c r="R6" t="n">
-        <v>6629645</v>
+        <v>6629580</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Hörde en spillkråka i närheten och dessaTydliga spår efter spillkråka som sökt föda.</t>
+          <t>Hjälp gärna till att artbestämma. Är ingen höjdare på vedsvampar?</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1302,7 +1302,27 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Blandskog</t>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1320,10 +1340,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121942431</v>
+        <v>121942119</v>
       </c>
       <c r="B7" t="n">
-        <v>91184</v>
+        <v>94662</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1332,25 +1352,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>2818</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1360,7 +1380,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>utan kapsel</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1369,10 +1394,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>357652</v>
+        <v>357630</v>
       </c>
       <c r="R7" t="n">
-        <v>6629580</v>
+        <v>6629615</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1399,27 +1424,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2025-01-04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Hjälp gärna till att artbestämma. Är ingen höjdare på vedsvampar?</t>
+          <t>2025-01-04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1436,24 +1446,14 @@
           <t>Gransumpskog</t>
         </is>
       </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Picea abies</t>
+          <t>Stump</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1474,7 +1474,7 @@
         <v>121942079</v>
       </c>
       <c r="B8" t="n">
-        <v>94655</v>
+        <v>94662</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
         <v>121941985</v>
       </c>
       <c r="B9" t="n">
-        <v>94751</v>
+        <v>94758</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1735,6 +1735,921 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>122135506</v>
+      </c>
+      <c r="B10" t="n">
+        <v>74676</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Gotjärnet, Gotjärnet, Vrm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>357640</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6629599</v>
+      </c>
+      <c r="S10" t="n">
+        <v>20</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-01-15</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-01-15</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Petrus Oledal</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Petrus Oledal</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>122137892</v>
+      </c>
+      <c r="B11" t="n">
+        <v>94758</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>210</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Buxbaumia viridis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Noret, Noret, Vrm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>357678</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6629579</v>
+      </c>
+      <c r="S11" t="n">
+        <v>20</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-01-15</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-01-15</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Petrus Oledal</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Petrus Oledal</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>122138961</v>
+      </c>
+      <c r="B12" t="n">
+        <v>78666</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>185</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Noret, Noret, Vrm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>357585</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6629645</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-01-15</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-01-15</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Petrus Oledal</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Petrus Oledal</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>122133273</v>
+      </c>
+      <c r="B13" t="n">
+        <v>94758</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>210</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Buxbaumia viridis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Gotjärnet, Gotjärnet, Vrm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>357582</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6629633</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-01-15</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-01-15</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Stump</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Petrus Oledal</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Petrus Oledal</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>122136904</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57518</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Noret, Noret, Vrm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>357834</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6629409</v>
+      </c>
+      <c r="S14" t="n">
+        <v>15</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-01-15</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-01-15</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Petrus Oledal</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Petrus Oledal</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>122135604</v>
+      </c>
+      <c r="B15" t="n">
+        <v>94758</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>210</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Buxbaumia viridis</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Gotjärnet, Gotjärnet, Vrm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>357645</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6629583</v>
+      </c>
+      <c r="S15" t="n">
+        <v>20</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-01-15</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-01-15</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Petrus Oledal</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Petrus Oledal</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>122135381</v>
+      </c>
+      <c r="B16" t="n">
+        <v>94662</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>2818</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Gotjärnet, Gotjärnet, Vrm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>357604</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6629595</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-01-15</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-01-15</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Petrus Oledal</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Petrus Oledal</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>122137168</v>
+      </c>
+      <c r="B17" t="n">
+        <v>94758</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>210</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Buxbaumia viridis</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Noret, Noret, Vrm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>357718</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6629315</v>
+      </c>
+      <c r="S17" t="n">
+        <v>20</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-01-15</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-01-15</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Petrus Oledal</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Petrus Oledal</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34188-2024 artfynd.xlsx
+++ b/artfynd/A 34188-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2651,6 +2651,118 @@
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>122179388</v>
+      </c>
+      <c r="B18" t="n">
+        <v>94767</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>210</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Buxbaumia viridis</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Gotjärnet, Gotjärnet, Vrm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>357804</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6629483</v>
+      </c>
+      <c r="S18" t="n">
+        <v>20</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-01-17</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-01-17</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Petrus Oledal</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Petrus Oledal</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34188-2024 artfynd.xlsx
+++ b/artfynd/A 34188-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>121895115</v>
       </c>
       <c r="B2" t="n">
-        <v>57365</v>
+        <v>57369</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>121895128</v>
       </c>
       <c r="B3" t="n">
-        <v>57518</v>
+        <v>57522</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>121895118</v>
       </c>
       <c r="B4" t="n">
-        <v>57734</v>
+        <v>57738</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>121942525</v>
       </c>
       <c r="B5" t="n">
-        <v>57381</v>
+        <v>57385</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1189,10 +1189,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121942431</v>
+        <v>121942119</v>
       </c>
       <c r="B6" t="n">
-        <v>91185</v>
+        <v>94671</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1201,25 +1201,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>2818</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1229,7 +1229,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>utan kapsel</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1238,10 +1243,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>357652</v>
+        <v>357630</v>
       </c>
       <c r="R6" t="n">
-        <v>6629580</v>
+        <v>6629615</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1268,27 +1273,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2025-01-04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Hjälp gärna till att artbestämma. Är ingen höjdare på vedsvampar?</t>
+          <t>2025-01-04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1305,24 +1295,14 @@
           <t>Gransumpskog</t>
         </is>
       </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Picea abies</t>
+          <t>Stump</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1340,10 +1320,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121942119</v>
+        <v>121942431</v>
       </c>
       <c r="B7" t="n">
-        <v>94662</v>
+        <v>91194</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1352,25 +1332,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2818</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1380,12 +1360,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>utan kapsel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1394,10 +1369,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>357630</v>
+        <v>357652</v>
       </c>
       <c r="R7" t="n">
-        <v>6629615</v>
+        <v>6629580</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1424,12 +1399,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-01-04</t>
+          <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-01-04</t>
+          <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Hjälp gärna till att artbestämma. Är ingen höjdare på vedsvampar?</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1446,14 +1436,24 @@
           <t>Gransumpskog</t>
         </is>
       </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Stump</t>
+          <t>Bark of dead wood # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1474,7 +1474,7 @@
         <v>121942079</v>
       </c>
       <c r="B8" t="n">
-        <v>94662</v>
+        <v>94671</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
         <v>121941985</v>
       </c>
       <c r="B9" t="n">
-        <v>94758</v>
+        <v>94767</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1738,10 +1738,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122135506</v>
+        <v>122135381</v>
       </c>
       <c r="B10" t="n">
-        <v>74676</v>
+        <v>94671</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1754,21 +1754,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6426</v>
+        <v>2818</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1778,13 +1778,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>357640</v>
+        <v>357604</v>
       </c>
       <c r="R10" t="n">
-        <v>6629599</v>
+        <v>6629595</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1853,7 +1853,7 @@
         <v>122137892</v>
       </c>
       <c r="B11" t="n">
-        <v>94758</v>
+        <v>94767</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1962,10 +1962,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122138961</v>
+        <v>122136904</v>
       </c>
       <c r="B12" t="n">
-        <v>78666</v>
+        <v>57522</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1978,21 +1978,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>185</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -2002,13 +2002,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>357585</v>
+        <v>357834</v>
       </c>
       <c r="R12" t="n">
-        <v>6629645</v>
+        <v>6629409</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2074,10 +2074,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122133273</v>
+        <v>122138961</v>
       </c>
       <c r="B13" t="n">
-        <v>94758</v>
+        <v>78673</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2086,47 +2086,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>210</v>
+        <v>185</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gotjärnet, Gotjärnet, Vrm</t>
+          <t>Noret, Noret, Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>357582</v>
+        <v>357585</v>
       </c>
       <c r="R13" t="n">
-        <v>6629633</v>
+        <v>6629645</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2158,7 +2149,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2168,7 +2159,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2179,16 +2170,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Stump</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2205,10 +2186,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122136904</v>
+        <v>122133273</v>
       </c>
       <c r="B14" t="n">
-        <v>57518</v>
+        <v>94767</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2217,41 +2198,50 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>210</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Noret, Noret, Vrm</t>
+          <t>Gotjärnet, Gotjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>357834</v>
+        <v>357582</v>
       </c>
       <c r="R14" t="n">
-        <v>6629409</v>
+        <v>6629633</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2280,7 +2270,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2290,7 +2280,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2301,6 +2291,16 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Stump</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2317,10 +2317,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122135604</v>
+        <v>122137168</v>
       </c>
       <c r="B15" t="n">
-        <v>94758</v>
+        <v>94767</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2353,14 +2353,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gotjärnet, Gotjärnet, Vrm</t>
+          <t>Noret, Noret, Vrm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>357645</v>
+        <v>357718</v>
       </c>
       <c r="R15" t="n">
-        <v>6629583</v>
+        <v>6629315</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2392,7 +2392,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2429,10 +2429,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122135381</v>
+        <v>122135506</v>
       </c>
       <c r="B16" t="n">
-        <v>94662</v>
+        <v>74680</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2445,21 +2445,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2818</v>
+        <v>6426</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2469,13 +2469,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>357604</v>
+        <v>357640</v>
       </c>
       <c r="R16" t="n">
-        <v>6629595</v>
+        <v>6629599</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2541,10 +2541,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122137168</v>
+        <v>122135604</v>
       </c>
       <c r="B17" t="n">
-        <v>94758</v>
+        <v>94767</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2577,14 +2577,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Noret, Noret, Vrm</t>
+          <t>Gotjärnet, Gotjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>357718</v>
+        <v>357645</v>
       </c>
       <c r="R17" t="n">
-        <v>6629315</v>
+        <v>6629583</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2616,7 +2616,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2763,6 +2763,210 @@
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>122209483</v>
+      </c>
+      <c r="B19" t="n">
+        <v>96682</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>2569</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Stor revmossa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Bazzania trilobata</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Noret, Noret, Vrm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>357695</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6629570</v>
+      </c>
+      <c r="S19" t="n">
+        <v>20</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-01-17</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-01-17</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Petrus Oledal</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Petrus Oledal</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>122209436</v>
+      </c>
+      <c r="B20" t="n">
+        <v>78673</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>185</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Noret, Noret, Vrm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>357735</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6629370</v>
+      </c>
+      <c r="S20" t="n">
+        <v>20</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-01-17</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-01-17</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Petrus Oledal</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Petrus Oledal</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34188-2024 artfynd.xlsx
+++ b/artfynd/A 34188-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2967,6 +2967,108 @@
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>122209688</v>
+      </c>
+      <c r="B21" t="n">
+        <v>96825</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>2605</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Stenporella</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Porella cordaeana</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Huebener) Moore</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Noret, Noret, Vrm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>357686</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6629621</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-01-18</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-01-18</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Petrus Oledal</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Petrus Oledal</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34188-2024 artfynd.xlsx
+++ b/artfynd/A 34188-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121895115</v>
+        <v>121895118</v>
       </c>
       <c r="B2" t="n">
-        <v>57369</v>
+        <v>57742</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -710,12 +710,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -725,14 +725,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Noret, Noret, Vrm</t>
+          <t>Gotjärnet, Gotjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>357630</v>
+        <v>357602</v>
       </c>
       <c r="R2" t="n">
-        <v>6629504</v>
+        <v>6629595</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -767,11 +767,6 @@
           <t>2024-12-30</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Såg endast en glimt av den och kunde inte säkert säga om det var Större Hackspett eller Tretåig. Men det lutade mer åt tretåig samt att en hel del skalade granar fanns i området. Och  många tecken på hackspettsaktivitet med hackhål i diverse torrakor.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -783,7 +778,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Barrskog i branter</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -804,7 +799,7 @@
         <v>121895128</v>
       </c>
       <c r="B3" t="n">
-        <v>57522</v>
+        <v>57525</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -937,10 +932,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121895118</v>
+        <v>121895115</v>
       </c>
       <c r="B4" t="n">
-        <v>57738</v>
+        <v>57372</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -949,20 +944,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -972,12 +967,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -987,14 +982,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gotjärnet, Gotjärnet, Vrm</t>
+          <t>Noret, Noret, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>357602</v>
+        <v>357630</v>
       </c>
       <c r="R4" t="n">
-        <v>6629595</v>
+        <v>6629504</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -1029,6 +1024,11 @@
           <t>2024-12-30</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Såg endast en glimt av den och kunde inte säkert säga om det var Större Hackspett eller Tretåig. Men det lutade mer åt tretåig samt att en hel del skalade granar fanns i området. Och  många tecken på hackspettsaktivitet med hackhål i diverse torrakor.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1040,7 +1040,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Barrskog i branter</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1061,7 +1061,7 @@
         <v>121942525</v>
       </c>
       <c r="B5" t="n">
-        <v>57385</v>
+        <v>57388</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>121942119</v>
       </c>
       <c r="B6" t="n">
-        <v>94671</v>
+        <v>94679</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>121942431</v>
       </c>
       <c r="B7" t="n">
-        <v>91194</v>
+        <v>91201</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1471,10 +1471,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121942079</v>
+        <v>121941985</v>
       </c>
       <c r="B8" t="n">
-        <v>94671</v>
+        <v>94775</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1487,36 +1487,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2818</v>
+        <v>210</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1525,10 +1520,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>357610</v>
+        <v>357622</v>
       </c>
       <c r="R8" t="n">
-        <v>6629638</v>
+        <v>6629654</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1558,19 +1553,9 @@
           <t>2024-12-30</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-12-30</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>15:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1612,10 +1597,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121941985</v>
+        <v>121942079</v>
       </c>
       <c r="B9" t="n">
-        <v>94767</v>
+        <v>94679</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1628,31 +1613,36 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>210</v>
+        <v>2818</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>kapslar</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1661,10 +1651,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>357622</v>
+        <v>357610</v>
       </c>
       <c r="R9" t="n">
-        <v>6629654</v>
+        <v>6629638</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1694,9 +1684,19 @@
           <t>2024-12-30</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1738,10 +1738,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122135381</v>
+        <v>122138961</v>
       </c>
       <c r="B10" t="n">
-        <v>94671</v>
+        <v>78677</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1750,41 +1750,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2818</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gotjärnet, Gotjärnet, Vrm</t>
+          <t>Noret, Noret, Vrm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>357604</v>
+        <v>357585</v>
       </c>
       <c r="R10" t="n">
-        <v>6629595</v>
+        <v>6629645</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1850,10 +1850,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122137892</v>
+        <v>122135506</v>
       </c>
       <c r="B11" t="n">
-        <v>94767</v>
+        <v>74684</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1866,34 +1866,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>210</v>
+        <v>6426</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Noret, Noret, Vrm</t>
+          <t>Gotjärnet, Gotjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>357678</v>
+        <v>357640</v>
       </c>
       <c r="R11" t="n">
-        <v>6629579</v>
+        <v>6629599</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1925,7 +1925,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1962,10 +1962,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122136904</v>
+        <v>122133273</v>
       </c>
       <c r="B12" t="n">
-        <v>57522</v>
+        <v>94775</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1974,41 +1974,50 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>210</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Noret, Noret, Vrm</t>
+          <t>Gotjärnet, Gotjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>357834</v>
+        <v>357582</v>
       </c>
       <c r="R12" t="n">
-        <v>6629409</v>
+        <v>6629633</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2037,7 +2046,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2047,7 +2056,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2058,6 +2067,16 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Stump</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2074,10 +2093,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122138961</v>
+        <v>122137168</v>
       </c>
       <c r="B13" t="n">
-        <v>78673</v>
+        <v>94775</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2086,25 +2105,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>185</v>
+        <v>210</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2114,13 +2133,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>357585</v>
+        <v>357718</v>
       </c>
       <c r="R13" t="n">
-        <v>6629645</v>
+        <v>6629315</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2149,7 +2168,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2159,7 +2178,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2186,10 +2205,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122133273</v>
+        <v>122137892</v>
       </c>
       <c r="B14" t="n">
-        <v>94767</v>
+        <v>94775</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2219,29 +2238,20 @@
           <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gotjärnet, Gotjärnet, Vrm</t>
+          <t>Noret, Noret, Vrm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>357582</v>
+        <v>357678</v>
       </c>
       <c r="R14" t="n">
-        <v>6629633</v>
+        <v>6629579</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2270,7 +2280,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2280,7 +2290,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2291,16 +2301,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Stump</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2317,10 +2317,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122137168</v>
+        <v>122135381</v>
       </c>
       <c r="B15" t="n">
-        <v>94767</v>
+        <v>94679</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2333,37 +2333,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>210</v>
+        <v>2818</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Noret, Noret, Vrm</t>
+          <t>Gotjärnet, Gotjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>357718</v>
+        <v>357604</v>
       </c>
       <c r="R15" t="n">
-        <v>6629315</v>
+        <v>6629595</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2429,10 +2429,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122135506</v>
+        <v>122135604</v>
       </c>
       <c r="B16" t="n">
-        <v>74680</v>
+        <v>94775</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2445,21 +2445,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6426</v>
+        <v>210</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2469,10 +2469,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>357640</v>
+        <v>357645</v>
       </c>
       <c r="R16" t="n">
-        <v>6629599</v>
+        <v>6629583</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2504,7 +2504,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2541,10 +2541,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122135604</v>
+        <v>122136904</v>
       </c>
       <c r="B17" t="n">
-        <v>94767</v>
+        <v>57525</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2553,41 +2553,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>210</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gotjärnet, Gotjärnet, Vrm</t>
+          <t>Noret, Noret, Vrm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>357645</v>
+        <v>357834</v>
       </c>
       <c r="R17" t="n">
-        <v>6629583</v>
+        <v>6629409</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2656,7 +2656,7 @@
         <v>122179388</v>
       </c>
       <c r="B18" t="n">
-        <v>94767</v>
+        <v>94775</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         <v>122209483</v>
       </c>
       <c r="B19" t="n">
-        <v>96682</v>
+        <v>96690</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
         <v>122209436</v>
       </c>
       <c r="B20" t="n">
-        <v>78673</v>
+        <v>78677</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         <v>122209688</v>
       </c>
       <c r="B21" t="n">
-        <v>96825</v>
+        <v>96833</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>

--- a/artfynd/A 34188-2024 artfynd.xlsx
+++ b/artfynd/A 34188-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121895118</v>
       </c>
       <c r="B2" t="n">
-        <v>57742</v>
+        <v>57744</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>121895128</v>
       </c>
       <c r="B3" t="n">
-        <v>57525</v>
+        <v>57527</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>121895115</v>
       </c>
       <c r="B4" t="n">
-        <v>57372</v>
+        <v>57374</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1058,10 +1058,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121942525</v>
+        <v>121942119</v>
       </c>
       <c r="B5" t="n">
-        <v>57388</v>
+        <v>94681</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1070,25 +1070,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>2818</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1096,9 +1096,14 @@
           <t>1</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>utan kapsel</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1107,10 +1112,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>357594</v>
+        <v>357630</v>
       </c>
       <c r="R5" t="n">
-        <v>6629645</v>
+        <v>6629615</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1137,27 +1142,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2025-01-04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Hörde en spillkråka i närheten och dessaTydliga spår efter spillkråka som sökt föda.</t>
+          <t>2025-01-04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1171,7 +1161,17 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Blandskog</t>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Stump</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1189,10 +1189,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121942119</v>
+        <v>121942525</v>
       </c>
       <c r="B6" t="n">
-        <v>94679</v>
+        <v>57390</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1201,25 +1201,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2818</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1227,14 +1227,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>utan kapsel</t>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1243,10 +1238,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>357630</v>
+        <v>357594</v>
       </c>
       <c r="R6" t="n">
-        <v>6629615</v>
+        <v>6629645</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1273,12 +1268,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-01-04</t>
+          <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-01-04</t>
+          <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Hörde en spillkråka i närheten och dessaTydliga spår efter spillkråka som sökt föda.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1292,17 +1302,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Stump</t>
+          <t>Blandskog</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1323,7 +1323,7 @@
         <v>121942431</v>
       </c>
       <c r="B7" t="n">
-        <v>91201</v>
+        <v>91203</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>121941985</v>
       </c>
       <c r="B8" t="n">
-        <v>94775</v>
+        <v>94777</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>121942079</v>
       </c>
       <c r="B9" t="n">
-        <v>94679</v>
+        <v>94681</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1738,10 +1738,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122138961</v>
+        <v>122135604</v>
       </c>
       <c r="B10" t="n">
-        <v>78677</v>
+        <v>94777</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1750,41 +1750,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>210</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Noret, Noret, Vrm</t>
+          <t>Gotjärnet, Gotjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>357585</v>
+        <v>357645</v>
       </c>
       <c r="R10" t="n">
-        <v>6629645</v>
+        <v>6629583</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1850,10 +1850,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122135506</v>
+        <v>122137892</v>
       </c>
       <c r="B11" t="n">
-        <v>74684</v>
+        <v>94777</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1866,34 +1866,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6426</v>
+        <v>210</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gotjärnet, Gotjärnet, Vrm</t>
+          <t>Noret, Noret, Vrm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>357640</v>
+        <v>357678</v>
       </c>
       <c r="R11" t="n">
-        <v>6629599</v>
+        <v>6629579</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1925,7 +1925,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1962,10 +1962,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122133273</v>
+        <v>122138961</v>
       </c>
       <c r="B12" t="n">
-        <v>94775</v>
+        <v>78679</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1974,47 +1974,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>210</v>
+        <v>185</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gotjärnet, Gotjärnet, Vrm</t>
+          <t>Noret, Noret, Vrm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>357582</v>
+        <v>357585</v>
       </c>
       <c r="R12" t="n">
-        <v>6629633</v>
+        <v>6629645</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2046,7 +2037,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2056,7 +2047,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2067,16 +2058,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Stump</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2093,10 +2074,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122137168</v>
+        <v>122135381</v>
       </c>
       <c r="B13" t="n">
-        <v>94775</v>
+        <v>94681</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2109,37 +2090,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>210</v>
+        <v>2818</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Noret, Noret, Vrm</t>
+          <t>Gotjärnet, Gotjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>357718</v>
+        <v>357604</v>
       </c>
       <c r="R13" t="n">
-        <v>6629315</v>
+        <v>6629595</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2168,7 +2149,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2178,7 +2159,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2205,10 +2186,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122137892</v>
+        <v>122135506</v>
       </c>
       <c r="B14" t="n">
-        <v>94775</v>
+        <v>74686</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2221,34 +2202,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>210</v>
+        <v>6426</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Noret, Noret, Vrm</t>
+          <t>Gotjärnet, Gotjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>357678</v>
+        <v>357640</v>
       </c>
       <c r="R14" t="n">
-        <v>6629579</v>
+        <v>6629599</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2280,7 +2261,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2290,7 +2271,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2317,10 +2298,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122135381</v>
+        <v>122136904</v>
       </c>
       <c r="B15" t="n">
-        <v>94679</v>
+        <v>57527</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2329,38 +2310,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2818</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gotjärnet, Gotjärnet, Vrm</t>
+          <t>Noret, Noret, Vrm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>357604</v>
+        <v>357834</v>
       </c>
       <c r="R15" t="n">
-        <v>6629595</v>
+        <v>6629409</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2392,7 +2373,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2402,7 +2383,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2429,10 +2410,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122135604</v>
+        <v>122133273</v>
       </c>
       <c r="B16" t="n">
-        <v>94775</v>
+        <v>94777</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2462,20 +2443,29 @@
           <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gotjärnet, Gotjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>357645</v>
+        <v>357582</v>
       </c>
       <c r="R16" t="n">
-        <v>6629583</v>
+        <v>6629633</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2504,7 +2494,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2514,7 +2504,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2525,6 +2515,16 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Stump</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2541,10 +2541,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122136904</v>
+        <v>122137168</v>
       </c>
       <c r="B17" t="n">
-        <v>57525</v>
+        <v>94777</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2553,25 +2553,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>210</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2581,13 +2581,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>357834</v>
+        <v>357718</v>
       </c>
       <c r="R17" t="n">
-        <v>6629409</v>
+        <v>6629315</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2656,7 +2656,7 @@
         <v>122179388</v>
       </c>
       <c r="B18" t="n">
-        <v>94775</v>
+        <v>94777</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2765,10 +2765,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122209483</v>
+        <v>122209436</v>
       </c>
       <c r="B19" t="n">
-        <v>96690</v>
+        <v>78679</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2777,25 +2777,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2569</v>
+        <v>185</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2805,10 +2805,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>357695</v>
+        <v>357735</v>
       </c>
       <c r="R19" t="n">
-        <v>6629570</v>
+        <v>6629370</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2867,10 +2867,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122209436</v>
+        <v>122209483</v>
       </c>
       <c r="B20" t="n">
-        <v>78677</v>
+        <v>96692</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2879,25 +2879,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>185</v>
+        <v>2569</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2907,10 +2907,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>357735</v>
+        <v>357695</v>
       </c>
       <c r="R20" t="n">
-        <v>6629370</v>
+        <v>6629570</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2972,7 +2972,7 @@
         <v>122209688</v>
       </c>
       <c r="B21" t="n">
-        <v>96833</v>
+        <v>96835</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>

--- a/artfynd/A 34188-2024 artfynd.xlsx
+++ b/artfynd/A 34188-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121895118</v>
+        <v>121895115</v>
       </c>
       <c r="B2" t="n">
-        <v>57744</v>
+        <v>57374</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -710,12 +710,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -725,14 +725,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gotjärnet, Gotjärnet, Vrm</t>
+          <t>Noret, Noret, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>357602</v>
+        <v>357630</v>
       </c>
       <c r="R2" t="n">
-        <v>6629595</v>
+        <v>6629504</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -767,6 +767,11 @@
           <t>2024-12-30</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Såg endast en glimt av den och kunde inte säkert säga om det var Större Hackspett eller Tretåig. Men det lutade mer åt tretåig samt att en hel del skalade granar fanns i området. Och  många tecken på hackspettsaktivitet med hackhål i diverse torrakor.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -778,7 +783,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Barrskog i branter</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -932,10 +937,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121895115</v>
+        <v>121895118</v>
       </c>
       <c r="B4" t="n">
-        <v>57374</v>
+        <v>57744</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -944,20 +949,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -967,12 +972,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -982,14 +987,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Noret, Noret, Vrm</t>
+          <t>Gotjärnet, Gotjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>357630</v>
+        <v>357602</v>
       </c>
       <c r="R4" t="n">
-        <v>6629504</v>
+        <v>6629595</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -1024,11 +1029,6 @@
           <t>2024-12-30</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Såg endast en glimt av den och kunde inte säkert säga om det var Större Hackspett eller Tretåig. Men det lutade mer åt tretåig samt att en hel del skalade granar fanns i området. Och  många tecken på hackspettsaktivitet med hackhål i diverse torrakor.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1040,7 +1040,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Barrskog i branter</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1738,7 +1738,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122135604</v>
+        <v>122133273</v>
       </c>
       <c r="B10" t="n">
         <v>94777</v>
@@ -1771,20 +1771,29 @@
           <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gotjärnet, Gotjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>357645</v>
+        <v>357582</v>
       </c>
       <c r="R10" t="n">
-        <v>6629583</v>
+        <v>6629633</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1813,7 +1822,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1823,7 +1832,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1834,6 +1843,16 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Stump</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1962,10 +1981,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122138961</v>
+        <v>122137168</v>
       </c>
       <c r="B12" t="n">
-        <v>78679</v>
+        <v>94777</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1974,25 +1993,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>185</v>
+        <v>210</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -2002,13 +2021,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>357585</v>
+        <v>357718</v>
       </c>
       <c r="R12" t="n">
-        <v>6629645</v>
+        <v>6629315</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2037,7 +2056,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2047,7 +2066,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2074,10 +2093,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122135381</v>
+        <v>122138961</v>
       </c>
       <c r="B13" t="n">
-        <v>94681</v>
+        <v>78679</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2086,41 +2105,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2818</v>
+        <v>185</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gotjärnet, Gotjärnet, Vrm</t>
+          <t>Noret, Noret, Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>357604</v>
+        <v>357585</v>
       </c>
       <c r="R13" t="n">
-        <v>6629595</v>
+        <v>6629645</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2149,7 +2168,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2159,7 +2178,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2410,10 +2429,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122133273</v>
+        <v>122135381</v>
       </c>
       <c r="B16" t="n">
-        <v>94777</v>
+        <v>94681</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2426,46 +2445,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>210</v>
+        <v>2818</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gotjärnet, Gotjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>357582</v>
+        <v>357604</v>
       </c>
       <c r="R16" t="n">
-        <v>6629633</v>
+        <v>6629595</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2494,7 +2504,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2504,7 +2514,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2515,16 +2525,6 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Stump</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2541,7 +2541,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122137168</v>
+        <v>122135604</v>
       </c>
       <c r="B17" t="n">
         <v>94777</v>
@@ -2577,14 +2577,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Noret, Noret, Vrm</t>
+          <t>Gotjärnet, Gotjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>357718</v>
+        <v>357645</v>
       </c>
       <c r="R17" t="n">
-        <v>6629315</v>
+        <v>6629583</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2616,7 +2616,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2765,10 +2765,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122209436</v>
+        <v>122209483</v>
       </c>
       <c r="B19" t="n">
-        <v>78679</v>
+        <v>96692</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2777,25 +2777,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>185</v>
+        <v>2569</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2805,10 +2805,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>357735</v>
+        <v>357695</v>
       </c>
       <c r="R19" t="n">
-        <v>6629370</v>
+        <v>6629570</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2867,10 +2867,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122209483</v>
+        <v>122209436</v>
       </c>
       <c r="B20" t="n">
-        <v>96692</v>
+        <v>78679</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2879,25 +2879,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2569</v>
+        <v>185</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2907,10 +2907,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>357695</v>
+        <v>357735</v>
       </c>
       <c r="R20" t="n">
-        <v>6629570</v>
+        <v>6629370</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>

--- a/artfynd/A 34188-2024 artfynd.xlsx
+++ b/artfynd/A 34188-2024 artfynd.xlsx
@@ -2205,10 +2205,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122135506</v>
+        <v>122136904</v>
       </c>
       <c r="B14" t="n">
-        <v>74686</v>
+        <v>57527</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2217,41 +2217,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6426</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gotjärnet, Gotjärnet, Vrm</t>
+          <t>Noret, Noret, Vrm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>357640</v>
+        <v>357834</v>
       </c>
       <c r="R14" t="n">
-        <v>6629599</v>
+        <v>6629409</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2317,10 +2317,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122136904</v>
+        <v>122135506</v>
       </c>
       <c r="B15" t="n">
-        <v>57527</v>
+        <v>74686</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2329,41 +2329,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>6426</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Noret, Noret, Vrm</t>
+          <t>Gotjärnet, Gotjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>357834</v>
+        <v>357640</v>
       </c>
       <c r="R15" t="n">
-        <v>6629409</v>
+        <v>6629599</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 34188-2024 artfynd.xlsx
+++ b/artfynd/A 34188-2024 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121895118</v>
+        <v>121895128</v>
       </c>
       <c r="B3" t="n">
-        <v>57744</v>
+        <v>57527</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,30 +813,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -851,17 +856,17 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gotjärnet, Gotjärnet, Vrm</t>
+          <t>Noret, Noret, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>357602</v>
+        <v>357721</v>
       </c>
       <c r="R3" t="n">
-        <v>6629595</v>
+        <v>6629323</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -888,11 +893,21 @@
           <t>2024-12-30</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-12-30</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -904,7 +919,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Barrskog i branter</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -922,10 +937,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121895128</v>
+        <v>121895118</v>
       </c>
       <c r="B4" t="n">
-        <v>57527</v>
+        <v>57744</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,35 +949,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -977,17 +987,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Noret, Noret, Vrm</t>
+          <t>Gotjärnet, Gotjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>357721</v>
+        <v>357602</v>
       </c>
       <c r="R4" t="n">
-        <v>6629323</v>
+        <v>6629595</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1014,21 +1024,11 @@
           <t>2024-12-30</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-12-30</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1040,7 +1040,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrskog i branter</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1058,10 +1058,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121942431</v>
+        <v>121942525</v>
       </c>
       <c r="B5" t="n">
-        <v>91219</v>
+        <v>57390</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1070,25 +1070,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1096,9 +1096,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1107,10 +1107,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>357652</v>
+        <v>357594</v>
       </c>
       <c r="R5" t="n">
-        <v>6629580</v>
+        <v>6629645</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1157,7 +1157,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Hjälp gärna till att artbestämma. Är ingen höjdare på vedsvampar?</t>
+          <t>Hörde en spillkråka i närheten och dessaTydliga spår efter spillkråka som sökt föda.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1171,27 +1171,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Picea abies</t>
+          <t>Blandskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1209,10 +1189,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121942119</v>
+        <v>121942431</v>
       </c>
       <c r="B6" t="n">
-        <v>94697</v>
+        <v>91219</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1221,25 +1201,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2818</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1249,12 +1229,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>utan kapsel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1263,10 +1238,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>357630</v>
+        <v>357652</v>
       </c>
       <c r="R6" t="n">
-        <v>6629615</v>
+        <v>6629580</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1293,12 +1268,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-01-04</t>
+          <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-01-04</t>
+          <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Hjälp gärna till att artbestämma. Är ingen höjdare på vedsvampar?</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1315,14 +1305,24 @@
           <t>Gransumpskog</t>
         </is>
       </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Stump</t>
+          <t>Bark of dead wood # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1340,10 +1340,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121942525</v>
+        <v>121942119</v>
       </c>
       <c r="B7" t="n">
-        <v>57390</v>
+        <v>94697</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1352,25 +1352,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>2818</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1378,9 +1378,14 @@
           <t>1</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>utan kapsel</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1389,10 +1394,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>357594</v>
+        <v>357630</v>
       </c>
       <c r="R7" t="n">
-        <v>6629645</v>
+        <v>6629615</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1419,27 +1424,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2025-01-04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Hörde en spillkråka i närheten och dessaTydliga spår efter spillkråka som sökt föda.</t>
+          <t>2025-01-04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1453,7 +1443,17 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Blandskog</t>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Stump</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1850,7 +1850,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122133273</v>
+        <v>122135604</v>
       </c>
       <c r="B11" t="n">
         <v>94793</v>
@@ -1883,29 +1883,20 @@
           <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gotjärnet, Gotjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>357582</v>
+        <v>357645</v>
       </c>
       <c r="R11" t="n">
-        <v>6629633</v>
+        <v>6629583</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1934,7 +1925,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1944,7 +1935,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1955,16 +1946,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Stump</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1981,7 +1962,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122137892</v>
+        <v>122137168</v>
       </c>
       <c r="B12" t="n">
         <v>94793</v>
@@ -2021,10 +2002,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>357678</v>
+        <v>357718</v>
       </c>
       <c r="R12" t="n">
-        <v>6629579</v>
+        <v>6629315</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -2056,7 +2037,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2066,7 +2047,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2205,10 +2186,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122135506</v>
+        <v>122136904</v>
       </c>
       <c r="B14" t="n">
-        <v>74686</v>
+        <v>57527</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2217,41 +2198,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6426</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gotjärnet, Gotjärnet, Vrm</t>
+          <t>Noret, Noret, Vrm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>357640</v>
+        <v>357834</v>
       </c>
       <c r="R14" t="n">
-        <v>6629599</v>
+        <v>6629409</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2280,7 +2261,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2290,7 +2271,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2317,7 +2298,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122137168</v>
+        <v>122137892</v>
       </c>
       <c r="B15" t="n">
         <v>94793</v>
@@ -2357,10 +2338,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>357718</v>
+        <v>357678</v>
       </c>
       <c r="R15" t="n">
-        <v>6629315</v>
+        <v>6629579</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2392,7 +2373,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2402,7 +2383,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2429,7 +2410,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122135604</v>
+        <v>122133273</v>
       </c>
       <c r="B16" t="n">
         <v>94793</v>
@@ -2462,20 +2443,29 @@
           <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gotjärnet, Gotjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>357645</v>
+        <v>357582</v>
       </c>
       <c r="R16" t="n">
-        <v>6629583</v>
+        <v>6629633</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2504,7 +2494,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2514,7 +2504,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2525,6 +2515,16 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Stump</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2541,10 +2541,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122136904</v>
+        <v>122135506</v>
       </c>
       <c r="B17" t="n">
-        <v>57527</v>
+        <v>74686</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2553,41 +2553,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>6426</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Noret, Noret, Vrm</t>
+          <t>Gotjärnet, Gotjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>357834</v>
+        <v>357640</v>
       </c>
       <c r="R17" t="n">
-        <v>6629409</v>
+        <v>6629599</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2765,10 +2765,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122209483</v>
+        <v>122209436</v>
       </c>
       <c r="B19" t="n">
-        <v>96708</v>
+        <v>78679</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2777,25 +2777,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2569</v>
+        <v>185</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2805,10 +2805,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>357695</v>
+        <v>357735</v>
       </c>
       <c r="R19" t="n">
-        <v>6629570</v>
+        <v>6629370</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2867,10 +2867,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122209436</v>
+        <v>122209483</v>
       </c>
       <c r="B20" t="n">
-        <v>78679</v>
+        <v>96708</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2879,25 +2879,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>185</v>
+        <v>2569</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2907,10 +2907,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>357735</v>
+        <v>357695</v>
       </c>
       <c r="R20" t="n">
-        <v>6629370</v>
+        <v>6629570</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>

--- a/artfynd/A 34188-2024 artfynd.xlsx
+++ b/artfynd/A 34188-2024 artfynd.xlsx
@@ -1058,10 +1058,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121942525</v>
+        <v>121942119</v>
       </c>
       <c r="B5" t="n">
-        <v>57390</v>
+        <v>94707</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1070,25 +1070,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>2818</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1096,9 +1096,14 @@
           <t>1</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>utan kapsel</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1107,10 +1112,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>357594</v>
+        <v>357630</v>
       </c>
       <c r="R5" t="n">
-        <v>6629645</v>
+        <v>6629615</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1137,27 +1142,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2025-01-04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Hörde en spillkråka i närheten och dessaTydliga spår efter spillkråka som sökt föda.</t>
+          <t>2025-01-04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1171,7 +1161,17 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Blandskog</t>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Stump</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1189,10 +1189,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121942431</v>
+        <v>121942525</v>
       </c>
       <c r="B6" t="n">
-        <v>91219</v>
+        <v>57390</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1201,25 +1201,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1227,9 +1227,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1238,10 +1238,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>357652</v>
+        <v>357594</v>
       </c>
       <c r="R6" t="n">
-        <v>6629580</v>
+        <v>6629645</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Hjälp gärna till att artbestämma. Är ingen höjdare på vedsvampar?</t>
+          <t>Hörde en spillkråka i närheten och dessaTydliga spår efter spillkråka som sökt föda.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1302,27 +1302,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Picea abies</t>
+          <t>Blandskog</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1340,10 +1320,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121942119</v>
+        <v>121942431</v>
       </c>
       <c r="B7" t="n">
-        <v>94697</v>
+        <v>91229</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1352,25 +1332,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2818</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1380,12 +1360,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>utan kapsel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1394,10 +1369,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>357630</v>
+        <v>357652</v>
       </c>
       <c r="R7" t="n">
-        <v>6629615</v>
+        <v>6629580</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1424,12 +1399,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-01-04</t>
+          <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-01-04</t>
+          <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Hjälp gärna till att artbestämma. Är ingen höjdare på vedsvampar?</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1446,14 +1436,24 @@
           <t>Gransumpskog</t>
         </is>
       </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Stump</t>
+          <t>Bark of dead wood # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1474,7 +1474,7 @@
         <v>121941985</v>
       </c>
       <c r="B8" t="n">
-        <v>94793</v>
+        <v>94803</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>121942079</v>
       </c>
       <c r="B9" t="n">
-        <v>94697</v>
+        <v>94707</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1738,10 +1738,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122135381</v>
+        <v>122133273</v>
       </c>
       <c r="B10" t="n">
-        <v>94697</v>
+        <v>94803</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1754,37 +1754,46 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2818</v>
+        <v>210</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gotjärnet, Gotjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>357604</v>
+        <v>357582</v>
       </c>
       <c r="R10" t="n">
-        <v>6629595</v>
+        <v>6629633</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1813,7 +1822,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1823,7 +1832,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1834,6 +1843,16 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Stump</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1850,10 +1869,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122135604</v>
+        <v>122138961</v>
       </c>
       <c r="B11" t="n">
-        <v>94793</v>
+        <v>78680</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1862,41 +1881,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>210</v>
+        <v>185</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gotjärnet, Gotjärnet, Vrm</t>
+          <t>Noret, Noret, Vrm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>357645</v>
+        <v>357585</v>
       </c>
       <c r="R11" t="n">
-        <v>6629583</v>
+        <v>6629645</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1925,7 +1944,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1935,7 +1954,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1965,7 +1984,7 @@
         <v>122137168</v>
       </c>
       <c r="B12" t="n">
-        <v>94793</v>
+        <v>94803</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2074,10 +2093,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122138961</v>
+        <v>122137892</v>
       </c>
       <c r="B13" t="n">
-        <v>78679</v>
+        <v>94803</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2086,25 +2105,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>185</v>
+        <v>210</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2114,13 +2133,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>357585</v>
+        <v>357678</v>
       </c>
       <c r="R13" t="n">
-        <v>6629645</v>
+        <v>6629579</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2149,7 +2168,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2159,7 +2178,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2186,10 +2205,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122136904</v>
+        <v>122135604</v>
       </c>
       <c r="B14" t="n">
-        <v>57527</v>
+        <v>94803</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2198,41 +2217,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>210</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Noret, Noret, Vrm</t>
+          <t>Gotjärnet, Gotjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>357834</v>
+        <v>357645</v>
       </c>
       <c r="R14" t="n">
-        <v>6629409</v>
+        <v>6629583</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2261,7 +2280,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2271,7 +2290,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2298,10 +2317,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122137892</v>
+        <v>122135381</v>
       </c>
       <c r="B15" t="n">
-        <v>94793</v>
+        <v>94707</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2314,37 +2333,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>210</v>
+        <v>2818</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Noret, Noret, Vrm</t>
+          <t>Gotjärnet, Gotjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>357678</v>
+        <v>357604</v>
       </c>
       <c r="R15" t="n">
-        <v>6629579</v>
+        <v>6629595</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2373,7 +2392,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2383,7 +2402,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2410,10 +2429,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122133273</v>
+        <v>122135506</v>
       </c>
       <c r="B16" t="n">
-        <v>94793</v>
+        <v>74686</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2426,46 +2445,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>210</v>
+        <v>6426</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gotjärnet, Gotjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>357582</v>
+        <v>357640</v>
       </c>
       <c r="R16" t="n">
-        <v>6629633</v>
+        <v>6629599</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2494,7 +2504,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2504,7 +2514,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2515,16 +2525,6 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Stump</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2541,10 +2541,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122135506</v>
+        <v>122136904</v>
       </c>
       <c r="B17" t="n">
-        <v>74686</v>
+        <v>57527</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2553,41 +2553,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6426</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gotjärnet, Gotjärnet, Vrm</t>
+          <t>Noret, Noret, Vrm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>357640</v>
+        <v>357834</v>
       </c>
       <c r="R17" t="n">
-        <v>6629599</v>
+        <v>6629409</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2656,7 +2656,7 @@
         <v>122179388</v>
       </c>
       <c r="B18" t="n">
-        <v>94793</v>
+        <v>94803</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         <v>122209436</v>
       </c>
       <c r="B19" t="n">
-        <v>78679</v>
+        <v>78680</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
         <v>122209483</v>
       </c>
       <c r="B20" t="n">
-        <v>96708</v>
+        <v>96718</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         <v>122209688</v>
       </c>
       <c r="B21" t="n">
-        <v>96851</v>
+        <v>96861</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>

--- a/artfynd/A 34188-2024 artfynd.xlsx
+++ b/artfynd/A 34188-2024 artfynd.xlsx
@@ -1058,10 +1058,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121942119</v>
+        <v>121942431</v>
       </c>
       <c r="B5" t="n">
-        <v>94707</v>
+        <v>91229</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1070,25 +1070,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2818</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1098,12 +1098,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>utan kapsel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1112,10 +1107,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>357630</v>
+        <v>357652</v>
       </c>
       <c r="R5" t="n">
-        <v>6629615</v>
+        <v>6629580</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1142,12 +1137,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-01-04</t>
+          <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-01-04</t>
+          <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Hjälp gärna till att artbestämma. Är ingen höjdare på vedsvampar?</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1164,14 +1174,24 @@
           <t>Gransumpskog</t>
         </is>
       </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Stump</t>
+          <t>Bark of dead wood # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1320,10 +1340,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121942431</v>
+        <v>121942119</v>
       </c>
       <c r="B7" t="n">
-        <v>91229</v>
+        <v>94707</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1332,25 +1352,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>2818</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1360,7 +1380,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>utan kapsel</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1369,10 +1394,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>357652</v>
+        <v>357630</v>
       </c>
       <c r="R7" t="n">
-        <v>6629580</v>
+        <v>6629615</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1399,27 +1424,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2025-01-04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Hjälp gärna till att artbestämma. Är ingen höjdare på vedsvampar?</t>
+          <t>2025-01-04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1436,24 +1446,14 @@
           <t>Gransumpskog</t>
         </is>
       </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Picea abies</t>
+          <t>Stump</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1471,10 +1471,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121941985</v>
+        <v>121942079</v>
       </c>
       <c r="B8" t="n">
-        <v>94803</v>
+        <v>94707</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1487,31 +1487,36 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>210</v>
+        <v>2818</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>kapslar</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1520,10 +1525,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>357622</v>
+        <v>357610</v>
       </c>
       <c r="R8" t="n">
-        <v>6629654</v>
+        <v>6629638</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1553,9 +1558,19 @@
           <t>2024-12-30</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1597,10 +1612,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121942079</v>
+        <v>121941985</v>
       </c>
       <c r="B9" t="n">
-        <v>94707</v>
+        <v>94803</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1613,36 +1628,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2818</v>
+        <v>210</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1651,10 +1661,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>357610</v>
+        <v>357622</v>
       </c>
       <c r="R9" t="n">
-        <v>6629638</v>
+        <v>6629654</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1684,19 +1694,9 @@
           <t>2024-12-30</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-12-30</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>15:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1738,10 +1738,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122133273</v>
+        <v>122135381</v>
       </c>
       <c r="B10" t="n">
-        <v>94803</v>
+        <v>94707</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1754,46 +1754,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>210</v>
+        <v>2818</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gotjärnet, Gotjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>357582</v>
+        <v>357604</v>
       </c>
       <c r="R10" t="n">
-        <v>6629633</v>
+        <v>6629595</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1822,7 +1813,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1832,7 +1823,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1843,16 +1834,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Stump</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1869,10 +1850,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122138961</v>
+        <v>122135604</v>
       </c>
       <c r="B11" t="n">
-        <v>78680</v>
+        <v>94803</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1881,41 +1862,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>185</v>
+        <v>210</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Noret, Noret, Vrm</t>
+          <t>Gotjärnet, Gotjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>357585</v>
+        <v>357645</v>
       </c>
       <c r="R11" t="n">
-        <v>6629645</v>
+        <v>6629583</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1944,7 +1925,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1954,7 +1935,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1981,7 +1962,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122137168</v>
+        <v>122137892</v>
       </c>
       <c r="B12" t="n">
         <v>94803</v>
@@ -2021,10 +2002,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>357718</v>
+        <v>357678</v>
       </c>
       <c r="R12" t="n">
-        <v>6629315</v>
+        <v>6629579</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -2056,7 +2037,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2066,7 +2047,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2093,10 +2074,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122137892</v>
+        <v>122135506</v>
       </c>
       <c r="B13" t="n">
-        <v>94803</v>
+        <v>74686</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2109,34 +2090,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>210</v>
+        <v>6426</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Noret, Noret, Vrm</t>
+          <t>Gotjärnet, Gotjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>357678</v>
+        <v>357640</v>
       </c>
       <c r="R13" t="n">
-        <v>6629579</v>
+        <v>6629599</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2168,7 +2149,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2178,7 +2159,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2205,7 +2186,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122135604</v>
+        <v>122133273</v>
       </c>
       <c r="B14" t="n">
         <v>94803</v>
@@ -2238,20 +2219,29 @@
           <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gotjärnet, Gotjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>357645</v>
+        <v>357582</v>
       </c>
       <c r="R14" t="n">
-        <v>6629583</v>
+        <v>6629633</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2280,7 +2270,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2290,7 +2280,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2301,6 +2291,16 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Stump</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2317,10 +2317,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122135381</v>
+        <v>122138961</v>
       </c>
       <c r="B15" t="n">
-        <v>94707</v>
+        <v>78680</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2329,41 +2329,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2818</v>
+        <v>185</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gotjärnet, Gotjärnet, Vrm</t>
+          <t>Noret, Noret, Vrm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>357604</v>
+        <v>357585</v>
       </c>
       <c r="R15" t="n">
-        <v>6629595</v>
+        <v>6629645</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2429,10 +2429,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122135506</v>
+        <v>122136904</v>
       </c>
       <c r="B16" t="n">
-        <v>74686</v>
+        <v>57527</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2441,41 +2441,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6426</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gotjärnet, Gotjärnet, Vrm</t>
+          <t>Noret, Noret, Vrm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>357640</v>
+        <v>357834</v>
       </c>
       <c r="R16" t="n">
-        <v>6629599</v>
+        <v>6629409</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2541,10 +2541,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122136904</v>
+        <v>122137168</v>
       </c>
       <c r="B17" t="n">
-        <v>57527</v>
+        <v>94803</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2553,25 +2553,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>210</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2581,13 +2581,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>357834</v>
+        <v>357718</v>
       </c>
       <c r="R17" t="n">
-        <v>6629409</v>
+        <v>6629315</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 34188-2024 artfynd.xlsx
+++ b/artfynd/A 34188-2024 artfynd.xlsx
@@ -1738,10 +1738,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122135381</v>
+        <v>122135506</v>
       </c>
       <c r="B10" t="n">
-        <v>94707</v>
+        <v>74691</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1754,21 +1754,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2818</v>
+        <v>6426</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1778,13 +1778,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>357604</v>
+        <v>357640</v>
       </c>
       <c r="R10" t="n">
-        <v>6629595</v>
+        <v>6629599</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1850,10 +1850,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122135604</v>
+        <v>122137168</v>
       </c>
       <c r="B11" t="n">
-        <v>94803</v>
+        <v>94815</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1886,14 +1886,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gotjärnet, Gotjärnet, Vrm</t>
+          <t>Noret, Noret, Vrm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>357645</v>
+        <v>357718</v>
       </c>
       <c r="R11" t="n">
-        <v>6629583</v>
+        <v>6629315</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1925,7 +1925,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1962,10 +1962,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122137892</v>
+        <v>122135381</v>
       </c>
       <c r="B12" t="n">
-        <v>94803</v>
+        <v>94719</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1978,37 +1978,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>210</v>
+        <v>2818</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Noret, Noret, Vrm</t>
+          <t>Gotjärnet, Gotjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>357678</v>
+        <v>357604</v>
       </c>
       <c r="R12" t="n">
-        <v>6629579</v>
+        <v>6629595</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2074,10 +2074,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122135506</v>
+        <v>122138961</v>
       </c>
       <c r="B13" t="n">
-        <v>74686</v>
+        <v>78685</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2086,41 +2086,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6426</v>
+        <v>185</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gotjärnet, Gotjärnet, Vrm</t>
+          <t>Noret, Noret, Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>357640</v>
+        <v>357585</v>
       </c>
       <c r="R13" t="n">
-        <v>6629599</v>
+        <v>6629645</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2186,10 +2186,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122133273</v>
+        <v>122137892</v>
       </c>
       <c r="B14" t="n">
-        <v>94803</v>
+        <v>94815</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2219,29 +2219,20 @@
           <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gotjärnet, Gotjärnet, Vrm</t>
+          <t>Noret, Noret, Vrm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>357582</v>
+        <v>357678</v>
       </c>
       <c r="R14" t="n">
-        <v>6629633</v>
+        <v>6629579</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2270,7 +2261,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2280,7 +2271,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2291,16 +2282,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Stump</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2317,10 +2298,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122138961</v>
+        <v>122135604</v>
       </c>
       <c r="B15" t="n">
-        <v>78680</v>
+        <v>94815</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2329,41 +2310,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>185</v>
+        <v>210</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Noret, Noret, Vrm</t>
+          <t>Gotjärnet, Gotjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>357585</v>
+        <v>357645</v>
       </c>
       <c r="R15" t="n">
-        <v>6629645</v>
+        <v>6629583</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2392,7 +2373,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2402,7 +2383,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2429,10 +2410,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122136904</v>
+        <v>122133273</v>
       </c>
       <c r="B16" t="n">
-        <v>57527</v>
+        <v>94815</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2441,41 +2422,50 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>210</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Noret, Noret, Vrm</t>
+          <t>Gotjärnet, Gotjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>357834</v>
+        <v>357582</v>
       </c>
       <c r="R16" t="n">
-        <v>6629409</v>
+        <v>6629633</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2504,7 +2494,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2514,7 +2504,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2525,6 +2515,16 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Stump</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2541,10 +2541,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122137168</v>
+        <v>122136904</v>
       </c>
       <c r="B17" t="n">
-        <v>94803</v>
+        <v>57532</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2553,25 +2553,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>210</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2581,13 +2581,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>357718</v>
+        <v>357834</v>
       </c>
       <c r="R17" t="n">
-        <v>6629315</v>
+        <v>6629409</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2656,7 +2656,7 @@
         <v>122179388</v>
       </c>
       <c r="B18" t="n">
-        <v>94803</v>
+        <v>94815</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         <v>122209436</v>
       </c>
       <c r="B19" t="n">
-        <v>78680</v>
+        <v>78685</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
         <v>122209483</v>
       </c>
       <c r="B20" t="n">
-        <v>96718</v>
+        <v>96730</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         <v>122209688</v>
       </c>
       <c r="B21" t="n">
-        <v>96861</v>
+        <v>96873</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>

--- a/artfynd/A 34188-2024 artfynd.xlsx
+++ b/artfynd/A 34188-2024 artfynd.xlsx
@@ -1738,10 +1738,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122135506</v>
+        <v>122136904</v>
       </c>
       <c r="B10" t="n">
-        <v>74691</v>
+        <v>57532</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1750,41 +1750,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6426</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gotjärnet, Gotjärnet, Vrm</t>
+          <t>Noret, Noret, Vrm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>357640</v>
+        <v>357834</v>
       </c>
       <c r="R10" t="n">
-        <v>6629599</v>
+        <v>6629409</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1850,10 +1850,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122137168</v>
+        <v>122135381</v>
       </c>
       <c r="B11" t="n">
-        <v>94815</v>
+        <v>94724</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1866,37 +1866,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>210</v>
+        <v>2818</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Noret, Noret, Vrm</t>
+          <t>Gotjärnet, Gotjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>357718</v>
+        <v>357604</v>
       </c>
       <c r="R11" t="n">
-        <v>6629315</v>
+        <v>6629595</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1962,10 +1962,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122135381</v>
+        <v>122135506</v>
       </c>
       <c r="B12" t="n">
-        <v>94719</v>
+        <v>74691</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1978,21 +1978,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2818</v>
+        <v>6426</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -2002,13 +2002,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>357604</v>
+        <v>357640</v>
       </c>
       <c r="R12" t="n">
-        <v>6629595</v>
+        <v>6629599</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2074,10 +2074,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122138961</v>
+        <v>122133273</v>
       </c>
       <c r="B13" t="n">
-        <v>78685</v>
+        <v>94820</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2086,38 +2086,47 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>185</v>
+        <v>210</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Noret, Noret, Vrm</t>
+          <t>Gotjärnet, Gotjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>357585</v>
+        <v>357582</v>
       </c>
       <c r="R13" t="n">
-        <v>6629645</v>
+        <v>6629633</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2149,7 +2158,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2159,7 +2168,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2170,6 +2179,16 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Stump</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2186,10 +2205,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122137892</v>
+        <v>122138961</v>
       </c>
       <c r="B14" t="n">
-        <v>94815</v>
+        <v>78685</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2198,25 +2217,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>210</v>
+        <v>185</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2226,13 +2245,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>357678</v>
+        <v>357585</v>
       </c>
       <c r="R14" t="n">
-        <v>6629579</v>
+        <v>6629645</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2261,7 +2280,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2271,7 +2290,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2298,10 +2317,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122135604</v>
+        <v>122137168</v>
       </c>
       <c r="B15" t="n">
-        <v>94815</v>
+        <v>94820</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2334,14 +2353,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gotjärnet, Gotjärnet, Vrm</t>
+          <t>Noret, Noret, Vrm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>357645</v>
+        <v>357718</v>
       </c>
       <c r="R15" t="n">
-        <v>6629583</v>
+        <v>6629315</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2373,7 +2392,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2383,7 +2402,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2410,10 +2429,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122133273</v>
+        <v>122137892</v>
       </c>
       <c r="B16" t="n">
-        <v>94815</v>
+        <v>94820</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2443,29 +2462,20 @@
           <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gotjärnet, Gotjärnet, Vrm</t>
+          <t>Noret, Noret, Vrm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>357582</v>
+        <v>357678</v>
       </c>
       <c r="R16" t="n">
-        <v>6629633</v>
+        <v>6629579</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2494,7 +2504,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2504,7 +2514,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2515,16 +2525,6 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Stump</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2541,10 +2541,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122136904</v>
+        <v>122135604</v>
       </c>
       <c r="B17" t="n">
-        <v>57532</v>
+        <v>94820</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2553,41 +2553,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>210</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Noret, Noret, Vrm</t>
+          <t>Gotjärnet, Gotjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>357834</v>
+        <v>357645</v>
       </c>
       <c r="R17" t="n">
-        <v>6629409</v>
+        <v>6629583</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2656,7 +2656,7 @@
         <v>122179388</v>
       </c>
       <c r="B18" t="n">
-        <v>94815</v>
+        <v>94820</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2765,10 +2765,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122209436</v>
+        <v>122209483</v>
       </c>
       <c r="B19" t="n">
-        <v>78685</v>
+        <v>96735</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2777,25 +2777,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>185</v>
+        <v>2569</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2805,10 +2805,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>357735</v>
+        <v>357695</v>
       </c>
       <c r="R19" t="n">
-        <v>6629370</v>
+        <v>6629570</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2867,10 +2867,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122209483</v>
+        <v>122209436</v>
       </c>
       <c r="B20" t="n">
-        <v>96730</v>
+        <v>78685</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2879,25 +2879,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2569</v>
+        <v>185</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2907,10 +2907,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>357695</v>
+        <v>357735</v>
       </c>
       <c r="R20" t="n">
-        <v>6629570</v>
+        <v>6629370</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2972,7 +2972,7 @@
         <v>122209688</v>
       </c>
       <c r="B21" t="n">
-        <v>96873</v>
+        <v>96878</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>

--- a/artfynd/A 34188-2024 artfynd.xlsx
+++ b/artfynd/A 34188-2024 artfynd.xlsx
@@ -1738,10 +1738,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122136904</v>
+        <v>122135604</v>
       </c>
       <c r="B10" t="n">
-        <v>57532</v>
+        <v>94829</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1750,41 +1750,36 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
+        <v>210</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Noret, Noret, Vrm</t>
+          <t>Gotjärnet, Gotjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>357834</v>
+        <v>357645</v>
       </c>
       <c r="R10" t="n">
-        <v>6629409</v>
+        <v>6629583</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1813,7 +1808,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1823,7 +1818,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1850,10 +1845,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122135381</v>
+        <v>122136904</v>
       </c>
       <c r="B11" t="n">
-        <v>94724</v>
+        <v>57532</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1862,38 +1857,33 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2818</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Stubbspretmossa</t>
-        </is>
+        <v>103021</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gotjärnet, Gotjärnet, Vrm</t>
+          <t>Noret, Noret, Vrm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>357604</v>
+        <v>357834</v>
       </c>
       <c r="R11" t="n">
-        <v>6629595</v>
+        <v>6629409</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1925,7 +1915,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1935,7 +1925,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1962,10 +1952,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122135506</v>
+        <v>122137168</v>
       </c>
       <c r="B12" t="n">
-        <v>74691</v>
+        <v>94829</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1978,34 +1968,29 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6426</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Kattfotslav</t>
-        </is>
+        <v>210</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gotjärnet, Gotjärnet, Vrm</t>
+          <t>Noret, Noret, Vrm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>357640</v>
+        <v>357718</v>
       </c>
       <c r="R12" t="n">
-        <v>6629599</v>
+        <v>6629315</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -2037,7 +2022,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2047,7 +2032,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2074,10 +2059,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122133273</v>
+        <v>122137892</v>
       </c>
       <c r="B13" t="n">
-        <v>94820</v>
+        <v>94829</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2092,11 +2077,6 @@
       <c r="E13" t="n">
         <v>210</v>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Grön sköldmossa</t>
-        </is>
-      </c>
       <c r="G13" t="inlineStr">
         <is>
           <t>Buxbaumia viridis</t>
@@ -2107,29 +2087,20 @@
           <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gotjärnet, Gotjärnet, Vrm</t>
+          <t>Noret, Noret, Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>357582</v>
+        <v>357678</v>
       </c>
       <c r="R13" t="n">
-        <v>6629633</v>
+        <v>6629579</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2158,7 +2129,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2168,7 +2139,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2179,16 +2150,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Stump</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2205,10 +2166,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122138961</v>
+        <v>122133273</v>
       </c>
       <c r="B14" t="n">
-        <v>78685</v>
+        <v>94829</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2217,38 +2178,42 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>185</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Violettgrå tagellav</t>
-        </is>
+        <v>210</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Noret, Noret, Vrm</t>
+          <t>Gotjärnet, Gotjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>357585</v>
+        <v>357582</v>
       </c>
       <c r="R14" t="n">
-        <v>6629645</v>
+        <v>6629633</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2280,7 +2245,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2290,7 +2255,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2301,6 +2266,16 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Stump</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2317,10 +2292,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122137168</v>
+        <v>122138961</v>
       </c>
       <c r="B15" t="n">
-        <v>94820</v>
+        <v>78686</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2329,25 +2304,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>210</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Grön sköldmossa</t>
-        </is>
+        <v>185</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2357,13 +2327,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>357718</v>
+        <v>357585</v>
       </c>
       <c r="R15" t="n">
-        <v>6629315</v>
+        <v>6629645</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2392,7 +2362,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2402,7 +2372,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2429,10 +2399,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122137892</v>
+        <v>122135381</v>
       </c>
       <c r="B16" t="n">
-        <v>94820</v>
+        <v>94733</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2445,37 +2415,32 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>210</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Grön sköldmossa</t>
-        </is>
+        <v>2818</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Noret, Noret, Vrm</t>
+          <t>Gotjärnet, Gotjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>357678</v>
+        <v>357604</v>
       </c>
       <c r="R16" t="n">
-        <v>6629579</v>
+        <v>6629595</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2504,7 +2469,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2514,7 +2479,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2541,10 +2506,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122135604</v>
+        <v>122135506</v>
       </c>
       <c r="B17" t="n">
-        <v>94820</v>
+        <v>74692</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2557,21 +2522,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>210</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Grön sköldmossa</t>
-        </is>
+        <v>6426</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2581,10 +2541,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>357645</v>
+        <v>357640</v>
       </c>
       <c r="R17" t="n">
-        <v>6629583</v>
+        <v>6629599</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2616,7 +2576,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2626,7 +2586,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2656,7 +2616,7 @@
         <v>122179388</v>
       </c>
       <c r="B18" t="n">
-        <v>94820</v>
+        <v>94829</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2670,11 +2630,6 @@
       </c>
       <c r="E18" t="n">
         <v>210</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Grön sköldmossa</t>
-        </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -2765,10 +2720,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122209483</v>
+        <v>122209436</v>
       </c>
       <c r="B19" t="n">
-        <v>96735</v>
+        <v>78686</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2777,25 +2732,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2569</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Stor revmossa</t>
-        </is>
+        <v>185</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2805,10 +2755,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>357695</v>
+        <v>357735</v>
       </c>
       <c r="R19" t="n">
-        <v>6629570</v>
+        <v>6629370</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2867,10 +2817,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122209436</v>
+        <v>122209483</v>
       </c>
       <c r="B20" t="n">
-        <v>78685</v>
+        <v>96744</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2879,25 +2829,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>185</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Violettgrå tagellav</t>
-        </is>
+        <v>2569</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2907,10 +2852,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>357735</v>
+        <v>357695</v>
       </c>
       <c r="R20" t="n">
-        <v>6629370</v>
+        <v>6629570</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2972,7 +2917,7 @@
         <v>122209688</v>
       </c>
       <c r="B21" t="n">
-        <v>96878</v>
+        <v>96887</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2986,11 +2931,6 @@
       </c>
       <c r="E21" t="n">
         <v>2605</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Stenporella</t>
-        </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>

--- a/artfynd/A 34188-2024 artfynd.xlsx
+++ b/artfynd/A 34188-2024 artfynd.xlsx
@@ -1738,10 +1738,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122135604</v>
+        <v>122137168</v>
       </c>
       <c r="B10" t="n">
-        <v>94829</v>
+        <v>94842</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1756,6 +1756,11 @@
       <c r="E10" t="n">
         <v>210</v>
       </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr">
         <is>
           <t>Buxbaumia viridis</t>
@@ -1769,14 +1774,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gotjärnet, Gotjärnet, Vrm</t>
+          <t>Noret, Noret, Vrm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>357645</v>
+        <v>357718</v>
       </c>
       <c r="R10" t="n">
-        <v>6629583</v>
+        <v>6629315</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1808,7 +1813,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1818,7 +1823,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1848,7 +1853,7 @@
         <v>122136904</v>
       </c>
       <c r="B11" t="n">
-        <v>57532</v>
+        <v>57536</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1862,6 +1867,11 @@
       </c>
       <c r="E11" t="n">
         <v>103021</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1952,10 +1962,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122137168</v>
+        <v>122135604</v>
       </c>
       <c r="B12" t="n">
-        <v>94829</v>
+        <v>94842</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1970,6 +1980,11 @@
       <c r="E12" t="n">
         <v>210</v>
       </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
       <c r="G12" t="inlineStr">
         <is>
           <t>Buxbaumia viridis</t>
@@ -1983,14 +1998,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Noret, Noret, Vrm</t>
+          <t>Gotjärnet, Gotjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>357718</v>
+        <v>357645</v>
       </c>
       <c r="R12" t="n">
-        <v>6629315</v>
+        <v>6629583</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -2022,7 +2037,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2032,7 +2047,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2059,10 +2074,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122137892</v>
+        <v>122133273</v>
       </c>
       <c r="B13" t="n">
-        <v>94829</v>
+        <v>94842</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2077,6 +2092,11 @@
       <c r="E13" t="n">
         <v>210</v>
       </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
       <c r="G13" t="inlineStr">
         <is>
           <t>Buxbaumia viridis</t>
@@ -2087,20 +2107,29 @@
           <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Noret, Noret, Vrm</t>
+          <t>Gotjärnet, Gotjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>357678</v>
+        <v>357582</v>
       </c>
       <c r="R13" t="n">
-        <v>6629579</v>
+        <v>6629633</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2129,7 +2158,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2139,7 +2168,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2150,6 +2179,16 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Stump</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2166,10 +2205,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122133273</v>
+        <v>122135381</v>
       </c>
       <c r="B14" t="n">
-        <v>94829</v>
+        <v>94746</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2182,41 +2221,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>210</v>
+        <v>2818</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gotjärnet, Gotjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>357582</v>
+        <v>357604</v>
       </c>
       <c r="R14" t="n">
-        <v>6629633</v>
+        <v>6629595</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2245,7 +2280,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2255,7 +2290,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2266,16 +2301,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Stump</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2292,10 +2317,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122138961</v>
+        <v>122135506</v>
       </c>
       <c r="B15" t="n">
-        <v>78686</v>
+        <v>74696</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2304,36 +2329,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>185</v>
+        <v>6426</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Noret, Noret, Vrm</t>
+          <t>Gotjärnet, Gotjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>357585</v>
+        <v>357640</v>
       </c>
       <c r="R15" t="n">
-        <v>6629645</v>
+        <v>6629599</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2362,7 +2392,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2372,7 +2402,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2399,10 +2429,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122135381</v>
+        <v>122137892</v>
       </c>
       <c r="B16" t="n">
-        <v>94733</v>
+        <v>94842</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2415,32 +2445,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2818</v>
+        <v>210</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gotjärnet, Gotjärnet, Vrm</t>
+          <t>Noret, Noret, Vrm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>357604</v>
+        <v>357678</v>
       </c>
       <c r="R16" t="n">
-        <v>6629595</v>
+        <v>6629579</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2469,7 +2504,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2479,7 +2514,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2506,10 +2541,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122135506</v>
+        <v>122138961</v>
       </c>
       <c r="B17" t="n">
-        <v>74692</v>
+        <v>78690</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2518,36 +2553,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6426</v>
+        <v>185</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gotjärnet, Gotjärnet, Vrm</t>
+          <t>Noret, Noret, Vrm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>357640</v>
+        <v>357585</v>
       </c>
       <c r="R17" t="n">
-        <v>6629599</v>
+        <v>6629645</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2576,7 +2616,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2586,7 +2626,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2616,7 +2656,7 @@
         <v>122179388</v>
       </c>
       <c r="B18" t="n">
-        <v>94829</v>
+        <v>94842</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2630,6 +2670,11 @@
       </c>
       <c r="E18" t="n">
         <v>210</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -2720,10 +2765,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122209436</v>
+        <v>122209483</v>
       </c>
       <c r="B19" t="n">
-        <v>78686</v>
+        <v>96757</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2732,20 +2777,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>185</v>
+        <v>2569</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Stor revmossa</t>
+        </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2755,10 +2805,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>357735</v>
+        <v>357695</v>
       </c>
       <c r="R19" t="n">
-        <v>6629370</v>
+        <v>6629570</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2817,10 +2867,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122209483</v>
+        <v>122209436</v>
       </c>
       <c r="B20" t="n">
-        <v>96744</v>
+        <v>78690</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2829,20 +2879,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2569</v>
+        <v>185</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2852,10 +2907,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>357695</v>
+        <v>357735</v>
       </c>
       <c r="R20" t="n">
-        <v>6629570</v>
+        <v>6629370</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2917,7 +2972,7 @@
         <v>122209688</v>
       </c>
       <c r="B21" t="n">
-        <v>96887</v>
+        <v>96900</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2931,6 +2986,11 @@
       </c>
       <c r="E21" t="n">
         <v>2605</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Stenporella</t>
+        </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>

--- a/artfynd/A 34188-2024 artfynd.xlsx
+++ b/artfynd/A 34188-2024 artfynd.xlsx
@@ -1738,10 +1738,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122137168</v>
+        <v>122138961</v>
       </c>
       <c r="B10" t="n">
-        <v>94842</v>
+        <v>78690</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1750,25 +1750,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>210</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1778,13 +1778,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>357718</v>
+        <v>357585</v>
       </c>
       <c r="R10" t="n">
-        <v>6629315</v>
+        <v>6629645</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1850,10 +1850,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122136904</v>
+        <v>122137892</v>
       </c>
       <c r="B11" t="n">
-        <v>57536</v>
+        <v>94855</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1862,25 +1862,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>210</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1890,13 +1890,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>357834</v>
+        <v>357678</v>
       </c>
       <c r="R11" t="n">
-        <v>6629409</v>
+        <v>6629579</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1962,10 +1962,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122135604</v>
+        <v>122135381</v>
       </c>
       <c r="B12" t="n">
-        <v>94842</v>
+        <v>94759</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1978,21 +1978,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>210</v>
+        <v>2818</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -2002,13 +2002,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>357645</v>
+        <v>357604</v>
       </c>
       <c r="R12" t="n">
-        <v>6629583</v>
+        <v>6629595</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2074,10 +2074,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122133273</v>
+        <v>122135604</v>
       </c>
       <c r="B13" t="n">
-        <v>94842</v>
+        <v>94855</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2107,29 +2107,20 @@
           <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gotjärnet, Gotjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>357582</v>
+        <v>357645</v>
       </c>
       <c r="R13" t="n">
-        <v>6629633</v>
+        <v>6629583</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2158,7 +2149,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2168,7 +2159,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2179,16 +2170,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Stump</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2205,10 +2186,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122135381</v>
+        <v>122135506</v>
       </c>
       <c r="B14" t="n">
-        <v>94746</v>
+        <v>74696</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2221,21 +2202,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2818</v>
+        <v>6426</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2245,13 +2226,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>357604</v>
+        <v>357640</v>
       </c>
       <c r="R14" t="n">
-        <v>6629595</v>
+        <v>6629599</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2280,7 +2261,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2290,7 +2271,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2317,10 +2298,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122135506</v>
+        <v>122137168</v>
       </c>
       <c r="B15" t="n">
-        <v>74696</v>
+        <v>94855</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2333,34 +2314,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6426</v>
+        <v>210</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gotjärnet, Gotjärnet, Vrm</t>
+          <t>Noret, Noret, Vrm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>357640</v>
+        <v>357718</v>
       </c>
       <c r="R15" t="n">
-        <v>6629599</v>
+        <v>6629315</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2392,7 +2373,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2402,7 +2383,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2429,10 +2410,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122137892</v>
+        <v>122133273</v>
       </c>
       <c r="B16" t="n">
-        <v>94842</v>
+        <v>94855</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2462,20 +2443,29 @@
           <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Noret, Noret, Vrm</t>
+          <t>Gotjärnet, Gotjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>357678</v>
+        <v>357582</v>
       </c>
       <c r="R16" t="n">
-        <v>6629579</v>
+        <v>6629633</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2504,7 +2494,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2514,7 +2504,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2525,6 +2515,16 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Stump</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2541,10 +2541,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122138961</v>
+        <v>122136904</v>
       </c>
       <c r="B17" t="n">
-        <v>78690</v>
+        <v>57536</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2557,21 +2557,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>185</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2581,13 +2581,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>357585</v>
+        <v>357834</v>
       </c>
       <c r="R17" t="n">
-        <v>6629645</v>
+        <v>6629409</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2656,7 +2656,7 @@
         <v>122179388</v>
       </c>
       <c r="B18" t="n">
-        <v>94842</v>
+        <v>94855</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         <v>122209483</v>
       </c>
       <c r="B19" t="n">
-        <v>96757</v>
+        <v>96770</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         <v>122209688</v>
       </c>
       <c r="B21" t="n">
-        <v>96900</v>
+        <v>96913</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>

--- a/artfynd/A 34188-2024 artfynd.xlsx
+++ b/artfynd/A 34188-2024 artfynd.xlsx
@@ -2972,7 +2972,7 @@
         <v>122209688</v>
       </c>
       <c r="B21" t="n">
-        <v>96913</v>
+        <v>96916</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>

--- a/artfynd/A 34188-2024 artfynd.xlsx
+++ b/artfynd/A 34188-2024 artfynd.xlsx
@@ -776,7 +776,7 @@
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG2" t="b">
         <v>0</v>
@@ -1164,7 +1164,7 @@
         <v>0</v>
       </c>
       <c r="AE5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG5" t="b">
         <v>0</v>
@@ -1830,7 +1830,7 @@
         <v>0</v>
       </c>
       <c r="AE10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG10" t="b">
         <v>0</v>
@@ -2278,7 +2278,7 @@
         <v>0</v>
       </c>
       <c r="AE14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG14" t="b">
         <v>0</v>

--- a/artfynd/A 34188-2024 artfynd.xlsx
+++ b/artfynd/A 34188-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121895115</v>
+        <v>122138961</v>
       </c>
       <c r="B2" t="n">
-        <v>57374</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,51 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Noret, Noret, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>357630</v>
+        <v>357585</v>
       </c>
       <c r="R2" t="n">
-        <v>6629504</v>
+        <v>6629645</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,17 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2025-01-15</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Såg endast en glimt av den och kunde inte säkert säga om det var Större Hackspett eller Tretåig. Men det lutade mer åt tretåig samt att en hel del skalade granar fanns i området. Och  många tecken på hackspettsaktivitet med hackhål i diverse torrakor.</t>
+          <t>2025-01-15</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,11 +766,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Gransumpskog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -801,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121895128</v>
+        <v>122209436</v>
       </c>
       <c r="B3" t="n">
-        <v>57527</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,56 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Noret, Noret, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>357721</v>
+        <v>357735</v>
       </c>
       <c r="R3" t="n">
-        <v>6629323</v>
+        <v>6629370</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -890,22 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>14:30</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:30</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,11 +863,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -937,67 +879,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121895118</v>
+        <v>122209442</v>
       </c>
       <c r="B4" t="n">
-        <v>57744</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gotjärnet, Gotjärnet, Vrm</t>
+          <t>Noret, Noret, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>357602</v>
+        <v>357626</v>
       </c>
       <c r="R4" t="n">
-        <v>6629595</v>
+        <v>6629487</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1021,12 +944,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1037,11 +960,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Barrskog i branter</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1058,37 +976,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121942431</v>
+        <v>121941985</v>
       </c>
       <c r="B5" t="n">
-        <v>91229</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>210</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1098,7 +1011,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1107,10 +1020,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>357652</v>
+        <v>357622</v>
       </c>
       <c r="R5" t="n">
-        <v>6629580</v>
+        <v>6629654</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1140,58 +1053,33 @@
           <t>2024-12-30</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-12-30</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Hjälp gärna till att artbestämma. Är ingen höjdare på vedsvampar?</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Blandskog</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Picea abies</t>
+          <t>Stump</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1209,37 +1097,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121942525</v>
+        <v>122133273</v>
       </c>
       <c r="B6" t="n">
-        <v>57390</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>210</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1247,9 +1130,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1258,13 +1141,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>357594</v>
+        <v>357582</v>
       </c>
       <c r="R6" t="n">
-        <v>6629645</v>
+        <v>6629633</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1288,27 +1171,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Hörde en spillkråka i närheten och dessaTydliga spår efter spillkråka som sökt föda.</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1320,9 +1198,14 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Stump</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1340,15 +1223,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121942119</v>
+        <v>122135604</v>
       </c>
       <c r="B7" t="n">
-        <v>94707</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,48 +1234,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2818</v>
+        <v>210</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>utan kapsel</t>
-        </is>
-      </c>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gotjärnet, Gotjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>357630</v>
+        <v>357645</v>
       </c>
       <c r="R7" t="n">
-        <v>6629615</v>
+        <v>6629583</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1424,12 +1288,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-01-04</t>
+          <t>2025-01-15</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-01-04</t>
+          <t>2025-01-15</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1440,21 +1314,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Gransumpskog</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Stump</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1471,15 +1330,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121942079</v>
+        <v>122137168</v>
       </c>
       <c r="B8" t="n">
-        <v>94707</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1487,48 +1341,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2818</v>
+        <v>210</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gotjärnet, Gotjärnet, Vrm</t>
+          <t>Noret, Noret, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>357610</v>
+        <v>357718</v>
       </c>
       <c r="R8" t="n">
-        <v>6629638</v>
+        <v>6629315</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1555,22 +1395,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1581,21 +1421,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Stump</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1612,15 +1437,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121941985</v>
+        <v>122137892</v>
       </c>
       <c r="B9" t="n">
-        <v>94803</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1645,26 +1465,17 @@
           <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gotjärnet, Gotjärnet, Vrm</t>
+          <t>Noret, Noret, Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>357622</v>
+        <v>357678</v>
       </c>
       <c r="R9" t="n">
-        <v>6629654</v>
+        <v>6629579</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1691,12 +1502,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2025-01-15</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2025-01-15</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1707,21 +1528,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Stump</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1738,53 +1544,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122138961</v>
+        <v>122179388</v>
       </c>
       <c r="B10" t="n">
-        <v>78690</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>210</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Noret, Noret, Vrm</t>
+          <t>Gotjärnet, Gotjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>357585</v>
+        <v>357804</v>
       </c>
       <c r="R10" t="n">
-        <v>6629645</v>
+        <v>6629483</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1808,29 +1609,29 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="b">
         <v>0</v>
@@ -1850,50 +1651,54 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122137892</v>
+        <v>121942431</v>
       </c>
       <c r="B11" t="n">
-        <v>94855</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>210</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Noret, Noret, Vrm</t>
+          <t>Gotjärnet, Gotjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>357678</v>
+        <v>357652</v>
       </c>
       <c r="R11" t="n">
-        <v>6629579</v>
+        <v>6629580</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1920,32 +1725,62 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Hjälp gärna till att artbestämma. Är ingen höjdare på vedsvampar?</t>
         </is>
       </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1962,15 +1797,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122135381</v>
+        <v>122209483</v>
       </c>
       <c r="B12" t="n">
-        <v>94759</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1978,37 +1808,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2818</v>
+        <v>2569</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gotjärnet, Gotjärnet, Vrm</t>
+          <t>Noret, Noret, Vrm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>357604</v>
+        <v>357695</v>
       </c>
       <c r="R12" t="n">
-        <v>6629595</v>
+        <v>6629570</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2032,22 +1862,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>13:45</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>13:45</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2074,15 +1894,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122135604</v>
+        <v>122209688</v>
       </c>
       <c r="B13" t="n">
-        <v>94855</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97812</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2090,37 +1905,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>210</v>
+        <v>2605</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stenporella</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Porella cordaeana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Huebener) Moore</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gotjärnet, Gotjärnet, Vrm</t>
+          <t>Noret, Noret, Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>357645</v>
+        <v>357686</v>
       </c>
       <c r="R13" t="n">
-        <v>6629583</v>
+        <v>6629621</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2144,22 +1959,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>14:01</t>
+          <t>2025-01-18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>14:01</t>
+          <t>2025-01-18</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2186,15 +1991,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122135506</v>
+        <v>121942079</v>
       </c>
       <c r="B14" t="n">
-        <v>74696</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96458</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2202,34 +2002,48 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6426</v>
+        <v>2818</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gotjärnet, Gotjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>357640</v>
+        <v>357610</v>
       </c>
       <c r="R14" t="n">
-        <v>6629599</v>
+        <v>6629638</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2256,32 +2070,47 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Stump</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2298,15 +2127,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122137168</v>
+        <v>121942119</v>
       </c>
       <c r="B15" t="n">
-        <v>94855</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96458</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2314,34 +2138,48 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>210</v>
+        <v>2818</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>utan kapsel</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Noret, Noret, Vrm</t>
+          <t>Gotjärnet, Gotjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>357718</v>
+        <v>357630</v>
       </c>
       <c r="R15" t="n">
-        <v>6629315</v>
+        <v>6629615</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2368,22 +2206,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>15:08</t>
+          <t>2025-01-04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>15:08</t>
+          <t>2025-01-04</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2394,6 +2222,21 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Stump</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2410,15 +2253,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122133273</v>
+        <v>122135381</v>
       </c>
       <c r="B16" t="n">
-        <v>94855</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96458</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2426,46 +2264,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>210</v>
+        <v>2818</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gotjärnet, Gotjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>357582</v>
+        <v>357604</v>
       </c>
       <c r="R16" t="n">
-        <v>6629633</v>
+        <v>6629595</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2494,7 +2323,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2504,7 +2333,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2515,16 +2344,6 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Stump</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2541,15 +2360,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122136904</v>
+        <v>122135506</v>
       </c>
       <c r="B17" t="n">
-        <v>57536</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2557,37 +2371,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>6426</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Noret, Noret, Vrm</t>
+          <t>Gotjärnet, Gotjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>357834</v>
+        <v>357640</v>
       </c>
       <c r="R17" t="n">
-        <v>6629409</v>
+        <v>6629599</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2616,7 +2430,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2626,14 +2440,14 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG17" t="b">
         <v>0</v>
@@ -2653,15 +2467,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122179388</v>
+        <v>121942525</v>
       </c>
       <c r="B18" t="n">
-        <v>94855</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2669,34 +2478,43 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>210</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Gotjärnet, Gotjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>357804</v>
+        <v>357594</v>
       </c>
       <c r="R18" t="n">
-        <v>6629483</v>
+        <v>6629645</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2723,22 +2541,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-01-17</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-01-17</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Hörde en spillkråka i närheten och dessaTydliga spår efter spillkråka som sökt föda.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2749,6 +2572,11 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2765,50 +2593,59 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122209483</v>
+        <v>121895115</v>
       </c>
       <c r="B19" t="n">
-        <v>96770</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2569</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Noret, Noret, Vrm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>357695</v>
+        <v>357630</v>
       </c>
       <c r="R19" t="n">
-        <v>6629570</v>
+        <v>6629504</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2835,22 +2672,32 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-01-17</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-01-17</t>
+          <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Såg endast en glimt av den och kunde inte säkert säga om det var Större Hackspett eller Tretåig. Men det lutade mer åt tretåig samt att en hel del skalade granar fanns i området. Och  många tecken på hackspettsaktivitet med hackhål i diverse torrakor.</t>
         </is>
       </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2867,50 +2714,59 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122209436</v>
+        <v>121895118</v>
       </c>
       <c r="B20" t="n">
-        <v>78690</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>185</v>
+        <v>103015</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Noret, Noret, Vrm</t>
+          <t>Gotjärnet, Gotjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>357735</v>
+        <v>357602</v>
       </c>
       <c r="R20" t="n">
-        <v>6629370</v>
+        <v>6629595</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2937,12 +2793,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-01-17</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-01-17</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2953,6 +2809,11 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Barrskog i branter</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2969,50 +2830,64 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122209688</v>
+        <v>121895128</v>
       </c>
       <c r="B21" t="n">
-        <v>96916</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2605</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stenporella</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porella cordaeana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Huebener) Moore</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Noret, Noret, Vrm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>357686</v>
+        <v>357721</v>
       </c>
       <c r="R21" t="n">
-        <v>6629621</v>
+        <v>6629323</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3039,12 +2914,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-01-18</t>
+          <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-01-18</t>
+          <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3055,6 +2940,11 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3068,6 +2958,113 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>122136904</v>
+      </c>
+      <c r="B22" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Noret, Noret, Vrm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>357834</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6629409</v>
+      </c>
+      <c r="S22" t="n">
+        <v>15</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-01-15</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-01-15</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Petrus Oledal</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Petrus Oledal</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
